--- a/CBT_2023_2회/산업안전기사_2023_2회_문항등록.xlsx
+++ b/CBT_2023_2회/산업안전기사_2023_2회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1471,17 +1471,17 @@
       </c>
       <c r="AG3" s="32" t="inlineStr">
         <is>
-          <t>흰색은 &lt;strong&gt;N9.5&lt;/strong&gt;다. &lt;strong&gt;N0.5 는 검은색&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전보건표지의 색도기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;색채&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;색도기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;용도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;빨간색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7.5R 4/14&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;금지 · 경고&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;노란색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5Y 8.5/12&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;경고&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파란색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5PB 4/10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지시&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;녹색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5G 4/10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;흰색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;N9.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;보조색&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;밝다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;검은색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;N0.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;보조색&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;어둡다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>흰색은 &lt;strong&gt;N9.5&lt;/strong&gt;다. &lt;strong&gt;N0.5는 검은색&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전보건표지의 색도기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;색채&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;색도기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;용도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;빨간색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7.5R 4/14&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;금지 · 경고&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;노란색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5Y 8.5/12&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;경고&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파란색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5PB 4/10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지시&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;녹색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5G 4/10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;흰색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;N9.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;보조색&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;밝다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;검은색&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;N0.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;보조색&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;어둡다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH3" s="32" t="inlineStr">
         <is>
-          <t>① 빨간색 7.5R 4/14 는 맞다.&lt;br&gt;② 노란색 5Y 8.5/12 도 맞다.&lt;br&gt;③ 파란색 2.5PB 4/10 도 맞다.</t>
+          <t>① 빨간색 7.5R 4/14는 맞다.&lt;br&gt;② 노란색 5Y 8.5/12 도 맞다.&lt;br&gt;③ 파란색 2.5PB 4/10 도 맞다.</t>
         </is>
       </c>
       <c r="AI3" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;산업안전보건법 시행규칙 별표8 — 안전보건표지의 색도기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;N 은 무채색(Neutral)&lt;/strong&gt;을 뜻하고 뒤의 숫자가 &lt;strong&gt;명도&lt;/strong&gt;다. &lt;strong&gt;9.5 는 거의 흰색, 0.5 는 거의 검은색&lt;/strong&gt;이다. 두 값을 바꿔 놓는 것이 단골 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;흰색 N9.5, 검은색 N0.5&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건법 시행규칙 시행 2026. 8. 1.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95%EC%8B%9C%ED%96%89%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건법 시행규칙 별표 8&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
+          <t>&lt;strong&gt;산업안전보건법 시행규칙 별표8 — 안전보건표지의 색도기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;N은 무채색(Neutral)&lt;/strong&gt;을 뜻하고 뒤의 숫자가 &lt;strong&gt;명도&lt;/strong&gt;다. &lt;strong&gt;9.5는 거의 흰색, 0.5는 거의 검은색&lt;/strong&gt;이다. 두 값을 바꿔 놓는 것이 단골 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;흰색 N9.5, 검은색 N0.5&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건법 시행규칙 시행 2026. 8. 1.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95%EC%8B%9C%ED%96%89%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건법 시행규칙 별표 8&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="AG4" s="32" t="inlineStr">
         <is>
-          <t>연근로시간은 $300 \times 8 \times 300 = 720 {,} 000$ 시간이다. 도수율은 $\dfrac{21}{720 {,} 000} \times 10^{6} \fallingdotseq 29.17$ 이고, 환산도수율은 $29.17 \times \dfrac{100 {,} 000}{10^{6}} \fallingdotseq 2.9$ 이므로 약 &lt;strong&gt;3건&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;환산강도율과 환산도수율&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;환산도수율&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;환산강도율&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;무엇&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;평생 몇 번 다치나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;평생 며칠을 잃나&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;식&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{도수율} \times \dfrac{\text{평생근로시간}}{10^{6}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{강도율} \times \dfrac{\text{평생근로시간}}{10^{3}}$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;평생 10만 시간&lt;/u&gt; (표준)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{도수율} \div 10$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{강도율} \times 100$&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>연근로시간은 $300 \times 8 \times 300 = 720 {,} 000$ 시간이다. 도수율은 $\dfrac{21}{720 {,} 000} \times 10^{6} \fallingdotseq 29.17$이고, 환산도수율은 $29.17 \times \dfrac{100 {,} 000}{10^{6}} \fallingdotseq 2.9$이므로 약 &lt;strong&gt;3건&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;환산강도율과 환산도수율&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;환산도수율&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;환산강도율&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;무엇&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;평생 몇 번 다치나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;평생 며칠을 잃나&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;식&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{도수율} \times \dfrac{\text{평생근로시간}}{10^{6}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{강도율} \times \dfrac{\text{평생근로시간}}{10^{3}}$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;평생 10만 시간&lt;/u&gt; (표준)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{도수율} \div 10$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{강도율} \times 100$&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH4" s="32" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AH5" s="32" t="inlineStr">
         <is>
-          <t>① Command Error 는 하려 해도 물자나 설비가 없어 못 하는 경우다.&lt;br&gt;② Primary Error 는 작업자 자신의 잘못이다.&lt;br&gt;④ 「Third Error」라는 갈래는 없다.</t>
+          <t>① Command Error는 하려 해도 물자나 설비가 없어 못 하는 경우다.&lt;br&gt;② Primary Error는 작업자 자신의 잘못이다.&lt;br&gt;④ 「Third Error」라는 갈래는 없다.</t>
         </is>
       </c>
       <c r="AI5" s="32" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="AH6" s="32" t="inlineStr">
         <is>
-          <t>② 5Y 8.5/12 는 노란색으로 그 밖의 위험경고에 쓴다.&lt;br&gt;③ 2.5PB 4/10 은 파란색으로 지시에 쓴다.&lt;br&gt;④ 2.5G 4/10 은 녹색으로 안내에 쓴다.</t>
+          <t>② 5Y 8.5/12는 노란색으로 그 밖의 위험경고에 쓴다.&lt;br&gt;③ 2.5PB 4/10은 파란색으로 지시에 쓴다.&lt;br&gt;④ 2.5G 4/10은 녹색으로 안내에 쓴다.</t>
         </is>
       </c>
       <c r="AI6" s="32" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="AI7" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;위험예지훈련 4라운드&lt;/strong&gt;&lt;br&gt;흐름은 &lt;strong&gt;보고 → 캐고 → 세우고 → 다짐한다&lt;/strong&gt;다. &lt;strong&gt;2R 에서 여러 위험 가운데 「진짜 위험한 것」을 골라 동그라미&lt;/strong&gt;를 친다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;현상파악 · 본질추구 · 대책수립 · 행동목표&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;위험예지훈련 4라운드&lt;/strong&gt;&lt;br&gt;흐름은 &lt;strong&gt;보고 → 캐고 → 세우고 → 다짐한다&lt;/strong&gt;다. &lt;strong&gt;2R에서 여러 위험 가운데 「진짜 위험한 것」을 골라 동그라미&lt;/strong&gt;를 친다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;현상파악 · 본질추구 · 대책수립 · 행동목표&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2113,12 +2113,12 @@
       </c>
       <c r="AH8" s="32" t="inlineStr">
         <is>
-          <t>① 14 [%] 는 이미 산소결핍 상태다.&lt;br&gt;② 16 [%] 도 그렇다.&lt;br&gt;④ 20 [%] 는 정상 공기에 가까운 값으로 기준보다 높다.</t>
+          <t>① 14 [%]는 이미 산소결핍 상태다.&lt;br&gt;② 16 [%] 도 그렇다.&lt;br&gt;④ 20 [%]는 정상 공기에 가까운 값으로 기준보다 높다.</t>
         </is>
       </c>
       <c r="AI8" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방독마스크의 사용 조건&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;방독마스크는 공기 속 유해가스만 걸러 낼 뿐 산소를 만들지 못한다&lt;/strong&gt;. &lt;strong&gt;산소가 모자란 곳에서 쓰면 오히려 질식&lt;/strong&gt; 한다. &lt;strong&gt;산소결핍의 경계가 18 [%]&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;산소 18 [%] 이상에서만 방독마스크&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방독마스크의 사용 조건&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;방독마스크는 공기 속 유해가스만 걸러 낼 뿐 산소를 만들지 못한다&lt;/strong&gt;. &lt;strong&gt;산소가 모자란 곳에서 쓰면 오히려 질식&lt;/strong&gt;한다. &lt;strong&gt;산소결핍의 경계가 18 [%]&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;산소 18 [%] 이상에서만 방독마스크&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="AG11" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;사생활에 큰 변화가 있는 사람은 사고를 낼 가능성이 높다&lt;/strong&gt;. &lt;strong&gt;마음이 다른 데 가 있어 의식이 우회&lt;/strong&gt; 하기 때문이다.</t>
+          <t>&lt;strong&gt;사생활에 큰 변화가 있는 사람은 사고를 낼 가능성이 높다&lt;/strong&gt;. &lt;strong&gt;마음이 다른 데 가 있어 의식이 우회&lt;/strong&gt;하기 때문이다.</t>
         </is>
       </c>
       <c r="AH11" s="32" t="inlineStr">
@@ -2882,17 +2882,17 @@
       </c>
       <c r="AG14" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Job Standardization Training&lt;/strong&gt;은 TWI 에 없다. 넷째는 &lt;strong&gt;Job Safety Training(JST)&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;TWI 의 네 가지 과정&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;과정&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;영문&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 가르치나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JIT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Instruction Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업을 가르치는 법&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JMT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Method Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업을 개선하는 법&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JRT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Relation Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사람을 다루는 법&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JST&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Safety Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전하게 일하는 법&lt;/u&gt; — Standardization 이 아니다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;Job Standardization Training&lt;/strong&gt;은 TWI에 없다. 넷째는 &lt;strong&gt;Job Safety Training(JST)&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;TWI의 네 가지 과정&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;과정&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;영문&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 가르치나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JIT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Instruction Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업을 가르치는 법&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JMT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Method Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업을 개선하는 법&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JRT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Relation Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사람을 다루는 법&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JST&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Safety Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전하게 일하는 법&lt;/u&gt; — Standardization이 아니다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH14" s="32" t="inlineStr">
         <is>
-          <t>① Job Method Training(JMT)은 TWI 의 과정이다.&lt;br&gt;② Job Relation Training(JRT)도 그렇다.&lt;br&gt;③ Job Instruction Training(JIT)도 그렇다.</t>
+          <t>① Job Method Training(JMT)은 TWI의 과정이다.&lt;br&gt;② Job Relation Training(JRT)도 그렇다.&lt;br&gt;③ Job Instruction Training(JIT)도 그렇다.</t>
         </is>
       </c>
       <c r="AI14" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;TWI(Training Within Industry)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;TWI 는 관리감독자를 위한 정형교육&lt;/strong&gt;으로 &lt;strong&gt;1회 10시간, 하루 2시간씩 5일&lt;/strong&gt;에 걸쳐 한다. 갈림길은 &lt;strong&gt;JST 의 S 가 Standardization 이 아니라 Safety&lt;/strong&gt;라는 데 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가르치고 · 고치고 · 다루고 · 안전하게&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;TWI(Training Within Industry)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;TWI는 관리감독자를 위한 정형교육&lt;/strong&gt;으로 &lt;strong&gt;1회 10시간, 하루 2시간씩 5일&lt;/strong&gt;에 걸쳐 한다. 갈림길은 &lt;strong&gt;JST의 S가 Standardization이 아니라 Safety&lt;/strong&gt;라는 데 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가르치고 · 고치고 · 다루고 · 안전하게&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3269,17 +3269,17 @@
       </c>
       <c r="AG17" s="32" t="inlineStr">
         <is>
-          <t>$B = f ( P \cdot E )$ 다. &lt;strong&gt;행동은 사람과 환경의 함수&lt;/strong&gt;라는 뜻이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;레빈의 법칙 $B = f ( P \cdot E )$&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Behavior 행동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;겉으로 드러나는 행동&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;f&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;function 함수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;P 와 E 가 함께 정한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;P&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Person 사람&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;나이 · 경험 · 성격 · 지능 · 심신 상태&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Environment 환경&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인간관계 · 작업환경 · 설비&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$B = f ( P \cdot E )$다. &lt;strong&gt;행동은 사람과 환경의 함수&lt;/strong&gt;라는 뜻이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;레빈의 법칙 $B = f ( P \cdot E )$&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Behavior 행동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;겉으로 드러나는 행동&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;f&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;function 함수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;P와 E가 함께 정한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;P&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Person 사람&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;나이 · 경험 · 성격 · 지능 · 심신 상태&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Environment 환경&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인간관계 · 작업환경 · 설비&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH17" s="32" t="inlineStr">
         <is>
-          <t>② $B = f ( P + 1 ) B$ 라는 식은 없다.&lt;br&gt;③ $P = E \cdot f ( B )$ 도 없다.&lt;br&gt;④ $E = f ( B + 1 ) P$ 도 없다.</t>
+          <t>② $B = f ( P + 1 ) B$라는 식은 없다.&lt;br&gt;③ $P = E \cdot f ( B )$도 없다.&lt;br&gt;④ $E = f ( B + 1 ) P$도 없다.</t>
         </is>
       </c>
       <c r="AI17" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;레빈(Lewin)의 인간 행동 법칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「행동(B)이 맨 앞에 오고, 괄호 안에 사람(P)과 환경(E)이 곱해져 있는」 것&lt;/strong&gt; 하나만 찾으면 된다. &lt;strong&gt;사람은 쉽게 못 바꾸지만 환경은 바꿀 수&lt;/strong&gt; 있으므로 안전관리는 E 를 손본다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $B = f ( P \cdot E )$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;레빈(Lewin)의 인간 행동 법칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「행동(B)이 맨 앞에 오고, 괄호 안에 사람(P)과 환경(E)이 곱해져 있는」 것&lt;/strong&gt; 하나만 찾으면 된다. &lt;strong&gt;사람은 쉽게 못 바꾸지만 환경은 바꿀 수&lt;/strong&gt; 있으므로 안전관리는 E를 손본다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $B = f ( P \cdot E )$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3398,12 +3398,12 @@
       </c>
       <c r="AG18" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;1 [%] 미만&lt;/strong&gt;이다. &lt;strong&gt;물에 담갔을 때 물을 빨아들이면 절연성능이 떨어지기&lt;/strong&gt; 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전모의 성능시험 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;시험&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내수성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질량 증가율 1 [%] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;AE · ABE&lt;/u&gt; (내전압성이 있는 것)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내전압성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;교류 20 [kV] 에서 1분간 견디고 누설전류 10 [mA] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;AE · ABE&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내관통성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관통거리 9.5 [mm] 이하&lt;/u&gt; (AE · ABE) · 11.1 [mm] 이하 (AB)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;충격흡수성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전달충격력 4,450 [N] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;1 [%] 미만&lt;/strong&gt;이다. &lt;strong&gt;물에 담갔을 때 물을 빨아들이면 절연성능이 떨어지기&lt;/strong&gt; 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전모의 성능시험 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;시험&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내수성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질량 증가율 1 [%] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;AE · ABE&lt;/u&gt; (내전압성이 있는 것)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내전압성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;교류 20 [kV]에서 1분간 견디고 누설전류 10 [mA] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;AE · ABE&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내관통성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관통거리 9.5 [mm] 이하&lt;/u&gt; (AE · ABE) · 11.1 [mm] 이하 (AB)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;충격흡수성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전달충격력 4,450 [N] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH18" s="32" t="inlineStr">
         <is>
-          <t>② 2 [%] 는 기준보다 느슨하다.&lt;br&gt;③ 3 [%] 도 그렇다.&lt;br&gt;④ 5 [%] 도 그렇다.</t>
+          <t>② 2 [%]는 기준보다 느슨하다.&lt;br&gt;③ 3 [%] 도 그렇다.&lt;br&gt;④ 5 [%] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI18" s="32" t="inlineStr">
@@ -3527,17 +3527,17 @@
       </c>
       <c r="AG19" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;영구일부노동불능은 등급별 손실일수를 그대로 쓴다&lt;/strong&gt;. &lt;strong&gt;300/365 를 곱하는 것은 일시적 노동불능(휴업일수)&lt;/strong&gt; 뿐이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;근로손실일수의 환산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;환산&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사망 · 1 ~ 3급&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7,500일&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;그대로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4 ~ 14급(영구일부노동불능)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;등급별 손실일수 그대로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300/365 를 곱하지 않는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일시 전노동불능(휴업)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;휴업일수 × 300/365&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연간 근로일수만 센다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;영구일부노동불능은 등급별 손실일수를 그대로 쓴다&lt;/strong&gt;. &lt;strong&gt;300/365를 곱하는 것은 일시적 노동불능(휴업일수)&lt;/strong&gt;뿐이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;근로손실일수의 환산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;환산&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사망 · 1 ~ 3급&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7,500일&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;그대로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4 ~ 14급(영구일부노동불능)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;등급별 손실일수 그대로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300/365를 곱하지 않는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일시 전노동불능(휴업)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;휴업일수 × 300/365&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연간 근로일수만 센다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH19" s="32" t="inlineStr">
         <is>
-          <t>① 사망 및 1 ~ 3급이 7,500일인 것은 맞다.&lt;br&gt;② 제14급이 50일인 것도 맞다.&lt;br&gt;④ 일시적 노동불능에 300/365 를 곱하는 것도 맞다.</t>
+          <t>① 사망 및 1 ~ 3급이 7,500일인 것은 맞다.&lt;br&gt;② 제14급이 50일인 것도 맞다.&lt;br&gt;④ 일시적 노동불능에 300/365를 곱하는 것도 맞다.</t>
         </is>
       </c>
       <c r="AI19" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;근로손실일수의 산정&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;300/365 를 곱하는 까닭은 「쉬는 날은 어차피 일하지 않으므로 빼자」&lt;/strong&gt;는 것이다. &lt;strong&gt;장해등급 손실일수는 이미 그 점을 감안해 정해 놓은 값&lt;/strong&gt;이라 다시 곱하지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;300/365 는 휴업일수에만&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;근로손실일수의 산정&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;300/365를 곱하는 까닭은 「쉬는 날은 어차피 일하지 않으므로 빼자」&lt;/strong&gt;는 것이다. &lt;strong&gt;장해등급 손실일수는 이미 그 점을 감안해 정해 놓은 값&lt;/strong&gt;이라 다시 곱하지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;300/365는 휴업일수에만&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3660,17 +3660,17 @@
       </c>
       <c r="AG20" s="32" t="inlineStr">
         <is>
-          <t>적발건수의 합은 &lt;strong&gt;7건&lt;/strong&gt;이고, 관찰한 연인원은 $100 \times 10 = 1 {,} 000$ 명이다. $\dfrac{7}{1 {,} 000} \times 100 = 0.7$ [%] 다.</t>
+          <t>적발건수의 합은 &lt;strong&gt;7건&lt;/strong&gt;이고, 관찰한 연인원은 $100 \times 10 = 1 {,} 000$ 명이다. $\dfrac{7}{1 {,} 000} \times 100 = 0.7$ [%]다.</t>
         </is>
       </c>
       <c r="AH20" s="32" t="inlineStr">
         <is>
-          <t>① 0.07 [%] 는 자릿수가 열 배 어긋난다.&lt;br&gt;③ 7 [%] 는 100 을 곱하지 않고 나눈 값이다.&lt;br&gt;④ 70 [%] 도 자릿수가 어긋난다.</t>
+          <t>① 0.07 [%]는 자릿수가 열 배 어긋난다.&lt;br&gt;③ 7 [%]는 100을 곱하지 않고 나눈 값이다.&lt;br&gt;④ 70 [%] 도 자릿수가 어긋난다.</t>
         </is>
       </c>
       <c r="AI20" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;불안전행동률&lt;/strong&gt;&lt;br&gt;$\text{불안전행동률} = \dfrac{\text{불안전행동 적발건수}}{\text{총 관찰인원}} \times 100$ 이다. &lt;strong&gt;분모는 「근로자 수 × 순회 횟수」&lt;/strong&gt;라는 점이 갈림길이다 — &lt;strong&gt;한 사람을 열 번 보면 열 번 센다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;적발건수 ÷ (인원 × 순회횟수)&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;불안전행동률&lt;/strong&gt;&lt;br&gt;$\text{불안전행동률} = \dfrac{\text{불안전행동 적발건수}}{\text{총 관찰인원}} \times 100$이다. &lt;strong&gt;분모는 「근로자 수 × 순회 횟수」&lt;/strong&gt;라는 점이 갈림길이다 — &lt;strong&gt;한 사람을 열 번 보면 열 번 센다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;적발건수 ÷ (인원 × 순회횟수)&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3789,12 +3789,12 @@
       </c>
       <c r="AG21" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;종합재해지수(FSI)&lt;/strong&gt;다. $\mathrm{FSI} = \sqrt{\text{도수율} \times \text{강도율}}$ 로 &lt;strong&gt;빈도와 강도를 함께&lt;/strong&gt; 본다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;재해율 지표&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지표&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;도수율 FR&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{재해건수}}{\text{연근로시간}} \times 10^{6}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;얼마나 자주&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도율 SR&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{근로손실일수}}{\text{연근로시간}} \times 10^{3}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;얼마나 심하게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;종합재해지수 FSI&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\sqrt{FR \times SR}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;둘의 기하평균&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;세이프 티 스코어&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{재해율의 차}}{\text{표준편차}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;과거와 현재의 비교&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;종합재해지수(FSI)&lt;/strong&gt;다. $\mathrm{FSI} = \sqrt{\text{도수율} \times \text{강도율}}$로 &lt;strong&gt;빈도와 강도를 함께&lt;/strong&gt; 본다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;재해율 지표&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지표&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;도수율 FR&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{재해건수}}{\text{연근로시간}} \times 10^{6}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;얼마나 자주&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도율 SR&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{근로손실일수}}{\text{연근로시간}} \times 10^{3}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;얼마나 심하게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;종합재해지수 FSI&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\sqrt{FR \times SR}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;둘의 기하평균&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;세이프 티 스코어&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{재해율의 차}}{\text{표준편차}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;과거와 현재의 비교&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH21" s="32" t="inlineStr">
         <is>
-          <t>① 강도율은 상해의 강약도만 나타낸다.&lt;br&gt;② 안전활동률은 안전활동의 정도를 나타내는 지표다.&lt;br&gt;③ safe-T-score 는 과거와 현재의 재해율을 견주는 지표다.</t>
+          <t>① 강도율은 상해의 강약도만 나타낸다.&lt;br&gt;② 안전활동률은 안전활동의 정도를 나타내는 지표다.&lt;br&gt;③ safe-T-score는 과거와 현재의 재해율을 견주는 지표다.</t>
         </is>
       </c>
       <c r="AI21" s="32" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AI22" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;하인리히의 재해손실비&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1 : 4 는 「직접비 : 간접비」&lt;/strong&gt;이므로 &lt;strong&gt;총액은 1 + 4 = 5배&lt;/strong&gt;다. &lt;strong&gt;간접비만 구하면 4배(32,000만원)&lt;/strong&gt;이라 그 보기가 함정으로 놓여 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;총 손실비용은 직접비의 5배&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;하인리히의 재해손실비&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1 : 4는 「직접비 : 간접비」&lt;/strong&gt;이므로 &lt;strong&gt;총액은 1 + 4 = 5배&lt;/strong&gt;다. &lt;strong&gt;간접비만 구하면 4배(32,000만원)&lt;/strong&gt;이라 그 보기가 함정으로 놓여 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;총 손실비용은 직접비의 5배&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4051,17 +4051,17 @@
       </c>
       <c r="AG23" s="32" t="inlineStr">
         <is>
-          <t>식으로 적으면 $T = A \cdot B = ( 1 + 2 ) ( 3 \cdot 1 )$ 다. 전개하면 $1 \cdot 3 \cdot 1 + 2 \cdot 3 \cdot 1 = 1 \cdot 3 + 1 \cdot 2 \cdot 3$ 인데, &lt;strong&gt;흡수법칙(&lt;/strong&gt;$A + AB = A$&lt;strong&gt;)&lt;/strong&gt;으로 &lt;strong&gt;{1, 3}&lt;/strong&gt;만 남는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;Fussell 알고리즘으로 컷셋 구하기&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;결과&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T = A · B (AND)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가로로 늘어놓는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;A B&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;A = 1 + 2 (OR)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;세로로 나눈다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 B / 2 B&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B = 3 · 1 (AND)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가로로 늘어놓는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 3 1 / 2 3 1&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;{1, 3} 과 {1, 2, 3}&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;{1,3} 이 {1,2,3} 에 포함되므로 최소는 {1,3}&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>식으로 적으면 $T = A \cdot B = ( 1 + 2 ) ( 3 \cdot 1 )$다. 전개하면 $1 \cdot 3 \cdot 1 + 2 \cdot 3 \cdot 1 = 1 \cdot 3 + 1 \cdot 2 \cdot 3$ 인데, &lt;strong&gt;흡수법칙(&lt;/strong&gt;$A + AB = A$&lt;strong&gt;)&lt;/strong&gt;으로 &lt;strong&gt;{1, 3}&lt;/strong&gt;만 남는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;Fussell 알고리즘으로 컷셋 구하기&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;결과&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T = A · B (AND)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가로로 늘어놓는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;A B&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;A = 1 + 2 (OR)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;세로로 나눈다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 B / 2 B&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B = 3 · 1 (AND)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가로로 늘어놓는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 3 1 / 2 3 1&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;{1, 3} 과 {1, 2, 3}&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;{1,3} 이 {1,2,3} 에 포함되므로 최소는 {1,3}&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH23" s="32" t="inlineStr">
         <is>
-          <t>① {1,2} 는 컷셋이 아니다 — B 가 일어나지 않으면 T 도 일어나지 않는다.&lt;br&gt;③ {2,3} 도 컷셋이 아니다 — 1 이 없으면 B 가 일어나지 않는다.&lt;br&gt;④ {1,2,3} 은 컷셋이지만 {1,3} 을 품고 있어 최소가 아니다.</t>
+          <t>① {1,2} 는 컷셋이 아니다 — B가 일어나지 않으면 T 도 일어나지 않는다.&lt;br&gt;③ {2,3} 도 컷셋이 아니다 — 1이 없으면 B가 일어나지 않는다.&lt;br&gt;④ {1,2,3} 은 컷셋이지만 {1,3} 을 품고 있어 최소가 아니다.</t>
         </is>
       </c>
       <c r="AI23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Fussell 알고리즘과 미니멀 컷셋&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;AND 게이트는 가로로, OR 게이트는 세로로&lt;/strong&gt; 늘어놓는 것이 Fussell 알고리즘이다. &lt;strong&gt;마지막에 남을 품고 있는 집합을 버리면&lt;/strong&gt; 미니멀 컷셋이 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;AND 는 가로, OR 는 세로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;Fussell 알고리즘과 미니멀 컷셋&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;AND 게이트는 가로로, OR 게이트는 세로로&lt;/strong&gt; 늘어놓는 것이 Fussell 알고리즘이다. &lt;strong&gt;마지막에 남을 품고 있는 집합을 버리면&lt;/strong&gt; 미니멀 컷셋이 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;AND는 가로, OR는 세로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,11 @@
           <t>마름모 모양의 사상기호 — 위아래로 선이 이어져 있다.</t>
         </is>
       </c>
-      <c r="W24" s="32" t="inlineStr"/>
+      <c r="W24" s="32" t="inlineStr">
+        <is>
+          <t>safe_A_2023_02_022_stem1.png</t>
+        </is>
+      </c>
       <c r="X24" s="32" t="inlineStr">
         <is>
           <t>시스템 분석에서 좀 더 발전시켜야 하는 사상</t>
@@ -4184,7 +4188,7 @@
       </c>
       <c r="AG24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;마름모는 생략사상&lt;/strong&gt;이다. &lt;strong&gt;정보가 모자라거나 중요하지 않아 더 캐지 않기로 한&lt;/strong&gt; 사상이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 의 사상기호&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;모양&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직사각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;결함사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;더 분석할 수 있는 사상&lt;/u&gt; — 정상사상과 중간사상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기본사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;더 분석할 수 없는 밑바닥 사상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;마름모&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생략사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;자료가 모자라 더 전개하지 않는 사상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;집 모양 오각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;통상사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;늘 일어나는 정상적인 사상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;삼각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전이기호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다른 곳으로 이어진다는 표시&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;마름모는 생략사상&lt;/strong&gt;이다. &lt;strong&gt;정보가 모자라거나 중요하지 않아 더 캐지 않기로 한&lt;/strong&gt; 사상이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA의 사상기호&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;모양&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직사각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;결함사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;더 분석할 수 있는 사상&lt;/u&gt; — 정상사상과 중간사상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기본사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;더 분석할 수 없는 밑바닥 사상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;마름모&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생략사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;자료가 모자라 더 전개하지 않는 사상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;집 모양 오각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;통상사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;늘 일어나는 정상적인 사상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;삼각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전이기호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다른 곳으로 이어진다는 표시&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH24" s="32" t="inlineStr">
@@ -4194,7 +4198,7 @@
       </c>
       <c r="AI24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 생략사상&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;기본사상(원)과 생략사상(마름모)&lt;/strong&gt;은 둘 다 &lt;strong&gt;더 전개하지 않는다&lt;/strong&gt;는 점이 같지만, &lt;strong&gt;원은 「더 캘 것이 없어서」, 마름모는 「캘 자료가 없어서」&lt;/strong&gt;라는 점이 다르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;마름모는 생략사상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 생략사상&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;기본사상(원)과 생략사상(마름모)&lt;/strong&gt;은 둘 다 &lt;strong&gt;더 전개하지 않는다&lt;/strong&gt;는 점이 같지만, &lt;strong&gt;원은 「더 캘 것이 없어서」, 마름모는 「캘 자료가 없어서」&lt;/strong&gt;라는 점이 다르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;마름모는 생략사상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4317,7 @@
       </c>
       <c r="AG25" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;패스셋은 시스템을 살리는 조합&lt;/strong&gt;이다. 나머지 셋은 모두 컷셋의 설명이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;컷셋과 패스셋&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;컷셋(cut set)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;패스셋(path set)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;무엇&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모두 일어나면 정상사상이 일어나는&lt;/u&gt; 조합&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모두 일어나지 않으면 정상사상이 일어나지 않는&lt;/u&gt; 조합&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;뜻&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시스템을 고장 내는 조합&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시스템을 살리는 조합&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;나타내는 것&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시스템의 약점 · 위험의 크기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시스템의 신뢰성&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;구하는 법&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Fussell 알고리즘&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;쌍대 FT 를 만들어 컷셋을 구한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;패스셋은 시스템을 살리는 조합&lt;/strong&gt;이다. 나머지 셋은 모두 컷셋의 설명이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;컷셋과 패스셋&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;컷셋(cut set)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;패스셋(path set)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;무엇&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모두 일어나면 정상사상이 일어나는&lt;/u&gt; 조합&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모두 일어나지 않으면 정상사상이 일어나지 않는&lt;/u&gt; 조합&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;뜻&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시스템을 고장 내는 조합&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시스템을 살리는 조합&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;나타내는 것&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시스템의 약점 · 위험의 크기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시스템의 신뢰성&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;구하는 법&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Fussell 알고리즘&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;쌍대 FT를 만들어 컷셋을 구한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH25" s="32" t="inlineStr">
@@ -4323,7 +4327,7 @@
       </c>
       <c r="AI25" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;미니멀 컷셋과 미니멀 패스셋&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;컷은 자른다(고장), 패스는 지나간다(정상)&lt;/strong&gt;로 새긴다. &lt;strong&gt;Fussell 알고리즘은 컷셋 전용&lt;/strong&gt;이며, &lt;strong&gt;패스셋은 AND 와 OR 를 뒤바꾼 쌍대 FT&lt;/strong&gt;를 만들어 구한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;컷은 고장, 패스는 정상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;미니멀 컷셋과 미니멀 패스셋&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;컷은 자른다(고장), 패스는 지나간다(정상)&lt;/strong&gt;로 새긴다. &lt;strong&gt;Fussell 알고리즘은 컷셋 전용&lt;/strong&gt;이며, &lt;strong&gt;패스셋은 AND와 OR를 뒤바꾼 쌍대 FT&lt;/strong&gt;를 만들어 구한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;컷은 고장, 패스는 정상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4681,12 +4685,12 @@
       </c>
       <c r="AH28" s="32" t="inlineStr">
         <is>
-          <t>① 30 [fc] 는 복도나 창고 같은 거친 작업의 수준이다.&lt;br&gt;③ 300 [fc] 는 제도나 타이핑 같은 정밀작업의 수준이다.&lt;br&gt;④ 500 [fc] 는 그 사이의 값으로 표준 구분에 없다.</t>
+          <t>① 30 [fc]는 복도나 창고 같은 거친 작업의 수준이다.&lt;br&gt;③ 300 [fc]는 제도나 타이핑 같은 정밀작업의 수준이다.&lt;br&gt;④ 500 [fc]는 그 사이의 값으로 표준 구분에 없다.</t>
         </is>
       </c>
       <c r="AI28" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;작업별 소요조명&lt;/strong&gt;&lt;br&gt;네 값이 &lt;strong&gt;30 → 100 → 300 → 1,000&lt;/strong&gt;으로 &lt;strong&gt;대략 세 배씩&lt;/strong&gt; 오른다. &lt;strong&gt;1 [fc] ≒ 10.8 [lux]&lt;/strong&gt;이므로 100 [fc] 는 약 1,080 [lux] 다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30 · 100 · 300 · 1,000 [fc]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;작업별 소요조명&lt;/strong&gt;&lt;br&gt;네 값이 &lt;strong&gt;30 → 100 → 300 → 1,000&lt;/strong&gt;으로 &lt;strong&gt;대략 세 배씩&lt;/strong&gt; 오른다. &lt;strong&gt;1 [fc] ≒ 10.8 [lux]&lt;/strong&gt;이므로 100 [fc]는 약 1,080 [lux]다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30 · 100 · 300 · 1,000 [fc]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4935,12 @@
       </c>
       <c r="AH30" s="32" t="inlineStr">
         <is>
-          <t>② FTA 는 설계·운전 단계의 정량적·연역적 기법이다.&lt;br&gt;③ FMEA 는 설계 단계의 귀납적 기법이다.&lt;br&gt;④ OSA 는 운용 단계의 분석이다.</t>
+          <t>② FTA는 설계·운전 단계의 정량적·연역적 기법이다.&lt;br&gt;③ FMEA는 설계 단계의 귀납적 기법이다.&lt;br&gt;④ OSA는 운용 단계의 분석이다.</t>
         </is>
       </c>
       <c r="AI30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;PHA(예비위험분석)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;PHA 의 P 가 Preliminary(예비)&lt;/strong&gt;다. &lt;strong&gt;아직 설계도 없는 구상 단계에서 「무엇이 위험할까」를 먼저 훑는&lt;/strong&gt; 것이라 가장 앞에 온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;구상단계의 첫 해석은 PHA&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;PHA(예비위험분석)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;PHA의 P가 Preliminary(예비)&lt;/strong&gt;다. &lt;strong&gt;아직 설계도 없는 구상 단계에서 「무엇이 위험할까」를 먼저 훑는&lt;/strong&gt; 것이라 가장 앞에 온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;구상단계의 첫 해석은 PHA&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5055,17 +5059,17 @@
       </c>
       <c r="AG31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;비용 효과 절충 분석&lt;/strong&gt;은 FMEA 의 절차가 아니다. &lt;strong&gt;돈 계산은 안전분석의 일이 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FMEA 의 실시 절차&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 하나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대상 시스템의 분석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;시스템 구성의 기본적 파악 · 기능 블록과 신뢰도 블록 다이어그램 작성&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고장 형태와 그 영향의 검토&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고장 등급의 평가 · 상위 체계에의 영향 분석&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;치명도 해석과 개선책 검토&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;비용 효과 절충 분석&lt;/strong&gt;은 FMEA의 절차가 아니다. &lt;strong&gt;돈 계산은 안전분석의 일이 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FMEA의 실시 절차&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 하나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대상 시스템의 분석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;시스템 구성의 기본적 파악 · 기능 블록과 신뢰도 블록 다이어그램 작성&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고장 형태와 그 영향의 검토&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고장 등급의 평가 · 상위 체계에의 영향 분석&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;치명도 해석과 개선책 검토&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH31" s="32" t="inlineStr">
         <is>
-          <t>② 시스템 구성의 기본적 파악은 FMEA 의 절차다.&lt;br&gt;③ 상위 체계에의 고장 영향 분석도 그렇다.&lt;br&gt;④ 신뢰도 블록 다이어그램 작성도 그렇다.</t>
+          <t>② 시스템 구성의 기본적 파악은 FMEA의 절차다.&lt;br&gt;③ 상위 체계에의 고장 영향 분석도 그렇다.&lt;br&gt;④ 신뢰도 블록 다이어그램 작성도 그렇다.</t>
         </is>
       </c>
       <c r="AI31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FMEA 의 실시 절차&lt;/strong&gt;&lt;br&gt;FMEA 는 &lt;strong&gt;「어떤 부품이 어떻게 고장 나면 위로 어떤 영향을 미치나」&lt;/strong&gt;를 따진다. &lt;strong&gt;「비용」·「효과」·「절충」&lt;/strong&gt; 같은 경영의 말이 나오면 대개 답이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비용 분석은 FMEA 의 절차가 아니다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FMEA의 실시 절차&lt;/strong&gt;&lt;br&gt;FMEA는 &lt;strong&gt;「어떤 부품이 어떻게 고장 나면 위로 어떤 영향을 미치나」&lt;/strong&gt;를 따진다. &lt;strong&gt;「비용」·「효과」·「절충」&lt;/strong&gt; 같은 경영의 말이 나오면 대개 답이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비용 분석은 FMEA의 절차가 아니다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5188,7 @@
       </c>
       <c r="AG32" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;자주보전활동단계&lt;/strong&gt;다. &lt;strong&gt;「내 설비는 내가 지킨다」&lt;/strong&gt;는 것이 자주보전의 뜻이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;TPM 의 주요 활동&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;활동&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;누가 무엇을&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자주보전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;운전자가 청소·급유·점검을 스스로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;개별개선&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;로스를 줄이는 개선 과제를 하나씩&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계획보전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보전 부서가 계획에 따라&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;품질보전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;불량이 나지 않는 조건을 지킨다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;교육훈련&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;운전자와 보전원의 기능을 높인다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;자주보전활동단계&lt;/strong&gt;다. &lt;strong&gt;「내 설비는 내가 지킨다」&lt;/strong&gt;는 것이 자주보전의 뜻이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;TPM의 주요 활동&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;활동&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;누가 무엇을&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자주보전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;운전자가 청소·급유·점검을 스스로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;개별개선&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;로스를 줄이는 개선 과제를 하나씩&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계획보전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보전 부서가 계획에 따라&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;품질보전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;불량이 나지 않는 조건을 지킨다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;교육훈련&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;운전자와 보전원의 기능을 높인다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH32" s="32" t="inlineStr">
@@ -5194,7 +5198,7 @@
       </c>
       <c r="AI32" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;TPM 의 자주보전&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「작업자 본인이 직접」·「일상에서」&lt;/strong&gt;라는 말이 자주보전을 가리킨다. &lt;strong&gt;청소 · 급유 · 조임 · 점검&lt;/strong&gt; 네 가지가 자주보전의 기본이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;내 설비는 내가 지키면 자주보전&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;TPM의 자주보전&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「작업자 본인이 직접」·「일상에서」&lt;/strong&gt;라는 말이 자주보전을 가리킨다. &lt;strong&gt;청소 · 급유 · 조임 · 점검&lt;/strong&gt; 네 가지가 자주보전의 기본이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;내 설비는 내가 지키면 자주보전&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5446,7 @@
       </c>
       <c r="AG34" s="32" t="inlineStr">
         <is>
-          <t>$R = \dfrac{T ( E - S )}{E - 1.5}$ 에 $T = 60$, $E = 6$, $S = 5$ 를 넣으면 $R = \dfrac{60 \times ( 6 - 5 )}{6 - 1.5} = \dfrac{60}{4.5} \fallingdotseq 13.3$ 분이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;머렐(Murrell)의 휴식시간 공식&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;휴식시간 [min]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;총 작업시간 [min]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업의 평균 에너지소비량 [kcal/min]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;S&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업에 대한 평균 에너지소비량의 상한&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;남성 5, 여성 3.5 [kcal/min]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;휴식 중 에너지소비량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고정값&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$R = \dfrac{T ( E - S )}{E - 1.5}$에 $T = 60$, $E = 6$, $S = 5$를 넣으면 $R = \dfrac{60 \times ( 6 - 5 )}{6 - 1.5} = \dfrac{60}{4.5} \fallingdotseq 13.3$ 분이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;머렐(Murrell)의 휴식시간 공식&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;휴식시간 [min]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;총 작업시간 [min]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업의 평균 에너지소비량 [kcal/min]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;S&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업에 대한 평균 에너지소비량의 상한&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;남성 5, 여성 3.5 [kcal/min]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;휴식 중 에너지소비량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고정값&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH34" s="32" t="inlineStr">
@@ -5452,7 +5456,7 @@
       </c>
       <c r="AI34" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;머렐(Murrell)의 휴식시간 산정&lt;/strong&gt;&lt;br&gt;$R = \dfrac{T ( E - S )}{E - 1.5}$ 다. &lt;strong&gt;분자는 「기준을 넘은 만큼」, 분모는 「쉬면 얼마나 회복되나」&lt;/strong&gt;를 뜻한다. $E \le S$&lt;strong&gt; 면 쉴 필요가 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $R = T ( E - S ) \div ( E - 1.5 )$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;머렐(Murrell)의 휴식시간 산정&lt;/strong&gt;&lt;br&gt;$R = \dfrac{T ( E - S )}{E - 1.5}$다. &lt;strong&gt;분자는 「기준을 넘은 만큼」, 분모는 「쉬면 얼마나 회복되나」&lt;/strong&gt;를 뜻한다. $E \le S$&lt;strong&gt;면 쉴 필요가 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $R = T ( E - S ) \div ( E - 1.5 )$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5714,7 @@
       </c>
       <c r="AI36" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;중이의 임피던스 정합&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;공기의 떨림을 액체(내이의 림프액)로 넘기려면 큰 힘이 필요&lt;/strong&gt; 하다. &lt;strong&gt;넓은 고막에서 좁은 난원창으로 힘을 모아&lt;/strong&gt; 그 손실을 메우는데, 이를 &lt;strong&gt;임피던스 정합&lt;/strong&gt;이라 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;중이에서 약 22배&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;중이의 임피던스 정합&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;공기의 떨림을 액체(내이의 림프액)로 넘기려면 큰 힘이 필요&lt;/strong&gt;하다. &lt;strong&gt;넓은 고막에서 좁은 난원창으로 힘을 모아&lt;/strong&gt; 그 손실을 메우는데, 이를 &lt;strong&gt;임피던스 정합&lt;/strong&gt;이라 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;중이에서 약 22배&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5833,7 @@
       </c>
       <c r="AG37" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;웨버의 법칙&lt;/strong&gt;이다. $\text{웨버비} = \dfrac{\Delta I}{I}$ 가 일정하다는 것이 그 뜻이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인간공학의 주요 법칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;법칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 말하나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;웨버 법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;변화감지역은 기준 자극의 크기에 비례&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\Delta I / I$ 가 일정&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;피츠 법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;표적이 작고 멀수록 이동시간이 길어진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$MT = a + b \log_{2} ( 2 A / W )$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;힉-하이만 법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;선택지가 많을수록 반응시간이 길어진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$RT = a + b \log_{2} N$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;신호검출이론&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;잡음 속에서 신호를 가려내는 판단&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;적중·오경보·누락·정기각&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;웨버의 법칙&lt;/strong&gt;이다. $\text{웨버비} = \dfrac{\Delta I}{I}$가 일정하다는 것이 그 뜻이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인간공학의 주요 법칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;법칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 말하나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;웨버 법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;변화감지역은 기준 자극의 크기에 비례&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\Delta I / I$가 일정&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;피츠 법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;표적이 작고 멀수록 이동시간이 길어진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$MT = a + b \log_{2} ( 2 A / W )$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;힉-하이만 법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;선택지가 많을수록 반응시간이 길어진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$RT = a + b \log_{2} N$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;신호검출이론&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;잡음 속에서 신호를 가려내는 판단&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;적중·오경보·누락·정기각&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH37" s="32" t="inlineStr">
@@ -6603,17 +6607,17 @@
       </c>
       <c r="AG43" s="32" t="inlineStr">
         <is>
-          <t>분할날의 최소길이는 $\dfrac{\pi D}{6}$ 로 &lt;strong&gt;톱날 원주의 1/6&lt;/strong&gt;이다. $\dfrac{\pi \times 500}{6} \fallingdotseq 262$ [mm] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;목재가공용 둥근톱 분할날의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최소 길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\pi D}{6}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱날 원주의 1/6 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;두께&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱날 두께의 1.1배 이상, 치진폭 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;톱날과의 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;12 [mm] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물리는 부분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱 뒷날의 2/3 이상을 덮을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>분할날의 최소길이는 $\dfrac{\pi D}{6}$로 &lt;strong&gt;톱날 원주의 1/6&lt;/strong&gt;이다. $\dfrac{\pi \times 500}{6} \fallingdotseq 262$ [mm]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;목재가공용 둥근톱 분할날의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최소 길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\pi D}{6}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱날 원주의 1/6 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;두께&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱날 두께의 1.1배 이상, 치진폭 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;톱날과의 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;12 [mm] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물리는 부분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱 뒷날의 2/3 이상을 덮을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH43" s="32" t="inlineStr">
         <is>
-          <t>① 462 [mm] 는 계산과 맞지 않는다.&lt;br&gt;② 362 [mm] 도 맞지 않는다.&lt;br&gt;④ 162 [mm] 도 맞지 않는다.</t>
+          <t>① 462 [mm]는 계산과 맞지 않는다.&lt;br&gt;② 362 [mm] 도 맞지 않는다.&lt;br&gt;④ 162 [mm] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI43" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;목재가공용 둥근톱의 분할날&lt;/strong&gt;&lt;br&gt;$\text{분할날 최소길이} = \dfrac{\pi D}{6}$ 다. &lt;strong&gt;톱날이 목재에 물려 있는 구간이 대략 원주의 1/6&lt;/strong&gt;이라 그만큼은 벌려 놓아야 반발을 막는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\text{분할날 길이} = \pi D \div 6$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;목재가공용 둥근톱의 분할날&lt;/strong&gt;&lt;br&gt;$\text{분할날 최소길이} = \dfrac{\pi D}{6}$다. &lt;strong&gt;톱날이 목재에 물려 있는 구간이 대략 원주의 1/6&lt;/strong&gt;이라 그만큼은 벌려 놓아야 반발을 막는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\text{분할날 길이} = \pi D \div 6$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7128,12 @@
       </c>
       <c r="AH47" s="32" t="inlineStr">
         <is>
-          <t>① 45 [cm] 는 기준에 못 미친다.&lt;br&gt;② 55 [cm] 도 그렇다.&lt;br&gt;④ 75 [cm] 는 기준보다 크다.</t>
+          <t>① 45 [cm]는 기준에 못 미친다.&lt;br&gt;② 55 [cm] 도 그렇다.&lt;br&gt;④ 75 [cm]는 기준보다 크다.</t>
         </is>
       </c>
       <c r="AI47" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제184조 — 구내운반차의 제동장치 등&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;핸들을 잡은 손이 차체 밖으로 나오지 않게&lt;/strong&gt; 하려면 &lt;strong&gt;핸들 중심에서 차체 끝까지 65 [cm] 이상&lt;/strong&gt;이 필요하다. 같은 조문에 &lt;strong&gt;전조등·후미등·경음기·후사경&lt;/strong&gt; 설치도 함께 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;핸들 중심에서 65 [cm] 이상&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 이 문항은 &lt;u&gt;개정 전 기준으로 출제&lt;/u&gt; 되었다. &lt;u&gt;구내운반차의 안전기준(규칙 제184조)&lt;/u&gt; 자체는 그대로이나, 조문 구성이 다시 정리되어 있으므로 &lt;u&gt;현행 조문으로 다시 확인&lt;/u&gt; 해 두는 것이 좋다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C184%EC%A1%B0" target="_blank"&gt;제184조(제동장치 등)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 구내운반차를 사용하는 경우에 다음 각 호의 사항을 준수해야 한다. &amp;lt;개정 2021.11.19, 2024.6.28&amp;gt;&lt;br&gt; 1. 주행을 제동하거나 정지상태를 유지하기 위하여 유효한 제동장치를 갖출 것&lt;br&gt; 2. 경음기를 갖출 것&lt;br&gt; 3. 운전석이 차 실내에 있는 것은 좌우에 한개씩 방향지시기를 갖출 것&lt;br&gt; 4. 전조등과 후미등을 갖출 것. 다만, 작업을 안전하게 하기 위하여 필요한 조명이 있는 장소에서 사용하는 구내운반차에 대해서는 그러하지 아니하다.&lt;br&gt; 5. 구내운반차가 후진 중에 주변의 근로자 또는 차량계하역운반기계등과 충돌할 위험이 있는 경우에는 구내운반차에 후진경보기와 경광등을 설치할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제184조 — 구내운반차의 제동장치 등&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;핸들을 잡은 손이 차체 밖으로 나오지 않게&lt;/strong&gt; 하려면 &lt;strong&gt;핸들 중심에서 차체 끝까지 65 [cm] 이상&lt;/strong&gt;이 필요하다. 같은 조문에 &lt;strong&gt;전조등·후미등·경음기·후사경&lt;/strong&gt; 설치도 함께 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;핸들 중심에서 65 [cm] 이상&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 이 문항은 &lt;u&gt;개정 전 기준으로 출제&lt;/u&gt; 되었다. &lt;u&gt;구내운반차의 안전기준(규칙 제184조)&lt;/u&gt; 자체는 그대로이나, 조문 구성이 다시 정리되어 있으므로 &lt;u&gt;현행 조문으로 다시 확인&lt;/u&gt;해 두는 것이 좋다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C184%EC%A1%B0" target="_blank"&gt;제184조(제동장치 등)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 구내운반차를 사용하는 경우에 다음 각 호의 사항을 준수해야 한다. &amp;lt;개정 2021.11.19, 2024.6.28&amp;gt;&lt;br&gt; 1. 주행을 제동하거나 정지상태를 유지하기 위하여 유효한 제동장치를 갖출 것&lt;br&gt; 2. 경음기를 갖출 것&lt;br&gt; 3. 운전석이 차 실내에 있는 것은 좌우에 한개씩 방향지시기를 갖출 것&lt;br&gt; 4. 전조등과 후미등을 갖출 것. 다만, 작업을 안전하게 하기 위하여 필요한 조명이 있는 장소에서 사용하는 구내운반차에 대해서는 그러하지 아니하다.&lt;br&gt; 5. 구내운반차가 후진 중에 주변의 근로자 또는 차량계하역운반기계등과 충돌할 위험이 있는 경우에는 구내운반차에 후진경보기와 경광등을 설치할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7262,7 @@
       </c>
       <c r="AI48" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제104조 — 금형조정작업의 위험 방지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정비할 때는 「전원을 끊는 것」만으로 부족&lt;/strong&gt; 하다. 유압이 빠지거나 자중으로 내려올 수 있으므로 &lt;strong&gt;물리적으로 괴어 두는 안전블록&lt;/strong&gt;이 필요하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;금형 조정에는 안전블록&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C104%EC%A1%B0" target="_blank"&gt;제104조(금형조정작업의 위험 방지)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;▶ 제104조(금형조정작업의 위험 방지) 사업주는 프레스등의 금형을 부착ㆍ해체 또는 조정하는 작업을 할 때에 해당 작업에 종사하는 근로자의 신체가 위험한계 내에 있는 경우 슬라이드가 갑자기 작동함으로써 근로자에게 발생할 우려가 있는 위험을 방지하기 위하여 &lt;strong&gt;안전블록&lt;/strong&gt;을 사용하는 등 필요한 조치를 하여야 한다.&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제104조 — 금형조정작업의 위험 방지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정비할 때는 「전원을 끊는 것」만으로 부족&lt;/strong&gt;하다. 유압이 빠지거나 자중으로 내려올 수 있으므로 &lt;strong&gt;물리적으로 괴어 두는 안전블록&lt;/strong&gt;이 필요하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;금형 조정에는 안전블록&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C104%EC%A1%B0" target="_blank"&gt;제104조(금형조정작업의 위험 방지)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;▶ 제104조(금형조정작업의 위험 방지) 사업주는 프레스등의 금형을 부착ㆍ해체 또는 조정하는 작업을 할 때에 해당 작업에 종사하는 근로자의 신체가 위험한계 내에 있는 경우 슬라이드가 갑자기 작동함으로써 근로자에게 발생할 우려가 있는 위험을 방지하기 위하여 &lt;strong&gt;안전블록&lt;/strong&gt;을 사용하는 등 필요한 조치를 하여야 한다.&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7768,7 @@
       </c>
       <c r="AG52" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;척 렌치를 빼고 시작&lt;/strong&gt; 해야 한다. &lt;strong&gt;꽂아 둔 채 돌리면 렌치가 튕겨 나가&lt;/strong&gt; 사람을 친다.</t>
+          <t>&lt;strong&gt;척 렌치를 빼고 시작&lt;/strong&gt;해야 한다. &lt;strong&gt;꽂아 둔 채 돌리면 렌치가 튕겨 나가&lt;/strong&gt; 사람을 친다.</t>
         </is>
       </c>
       <c r="AH52" s="32" t="inlineStr">
@@ -7893,7 +7897,7 @@
       </c>
       <c r="AG53" s="32" t="inlineStr">
         <is>
-          <t>상부틀 개구의 폭이나 길이는 &lt;strong&gt;16 [cm] 미만&lt;/strong&gt; 이라야 한다. &lt;strong&gt;「20 [cm] 이상」&lt;/strong&gt;은 크기와 방향이 모두 어긋난다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차 헤드가드의 기준 (규칙 제180조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최대하중의 2배(4 [t] 을 넘는 값은 4 [t])의 등분포정하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상부틀 개구의 폭·길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;16 [cm] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「20 [cm] 이상」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;앉아서 조작 — 좌석 윗면에서 상부틀 아랫면까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;서서 조작 — 운전석 바닥면에서 상부틀 아랫면까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>상부틀 개구의 폭이나 길이는 &lt;strong&gt;16 [cm] 미만&lt;/strong&gt;이라야 한다. &lt;strong&gt;「20 [cm] 이상」&lt;/strong&gt;은 크기와 방향이 모두 어긋난다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차 헤드가드의 기준 (규칙 제180조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최대하중의 2배(4 [t]을 넘는 값은 4 [t])의 등분포정하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상부틀 개구의 폭·길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;16 [cm] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「20 [cm] 이상」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;앉아서 조작 — 좌석 윗면에서 상부틀 아랫면까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;서서 조작 — 운전석 바닥면에서 상부틀 아랫면까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH53" s="32" t="inlineStr">
@@ -7903,7 +7907,7 @@
       </c>
       <c r="AI53" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제180조 — 헤드가드&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;16 [cm] 미만&lt;/strong&gt;은 &lt;strong&gt;머리가 빠져나가지 못하는 크기&lt;/strong&gt;다. &lt;strong&gt;구멍이 크면 떨어진 물체가 그대로 들어온다&lt;/strong&gt;는 점에서 「이상」이 될 수 없다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;개구는 16 [cm] 미만&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 이 문항은 &lt;u&gt;개정 전 기준으로 출제&lt;/u&gt; 되었으나, &lt;u&gt;규칙 제180조의 네 기준(2배 · 16 [cm] 미만 · 1 [m] · 2 [m])은 지금도 같다&lt;/u&gt;. 다만 &lt;u&gt;「최대하중」이 「최대하중의 2배 값(4 [t] 을 넘는 값에 대해서는 4 [t])」&lt;/u&gt;으로 조문이 다듬어졌다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C180%EC%A1%B0" target="_blank"&gt;제180조(헤드가드)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 다음 각 호에 따른 적합한 헤드가드(head guard)를 갖추지 아니한 지게차를 사용해서는 안 된다. 다만, 화물의 낙하에 의하여 지게차의 운전자에게 위험을 미칠 우려가 없는 경우에는 그렇지 않다. &amp;lt;개정 2019.1.31, 2022.10.18&amp;gt;&lt;br&gt;▶  1. 강도는 지게차의 최대하중의 2배 값(4톤&lt;strong&gt;을 넘는 값에 대해서는 4&lt;/strong&gt;톤으로 한다)의 등분포정하중(等分布靜荷重)에 견딜 수 있을 것&lt;br&gt;▶  2. &lt;strong&gt;상부틀의 각 개구의 폭 또는 길이가&lt;/strong&gt; 16센티미터 미만일 것&lt;br&gt; 3. 운전자가 앉아서 조작하거나 서서 조작하는 지게차의 헤드가드는 한국산업표준에서 정하는 높이 기준 이상일 것&lt;br&gt; 4. 삭제&amp;lt;2019.1.31&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제180조 — 헤드가드&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;16 [cm] 미만&lt;/strong&gt;은 &lt;strong&gt;머리가 빠져나가지 못하는 크기&lt;/strong&gt;다. &lt;strong&gt;구멍이 크면 떨어진 물체가 그대로 들어온다&lt;/strong&gt;는 점에서 「이상」이 될 수 없다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;개구는 16 [cm] 미만&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 이 문항은 &lt;u&gt;개정 전 기준으로 출제&lt;/u&gt; 되었으나, &lt;u&gt;규칙 제180조의 네 기준(2배 · 16 [cm] 미만 · 1 [m] · 2 [m])은 지금도 같다&lt;/u&gt;. 다만 &lt;u&gt;「최대하중」이 「최대하중의 2배 값(4 [t]을 넘는 값에 대해서는 4 [t])」&lt;/u&gt;으로 조문이 다듬어졌다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C180%EC%A1%B0" target="_blank"&gt;제180조(헤드가드)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 다음 각 호에 따른 적합한 헤드가드(head guard)를 갖추지 아니한 지게차를 사용해서는 안 된다. 다만, 화물의 낙하에 의하여 지게차의 운전자에게 위험을 미칠 우려가 없는 경우에는 그렇지 않다. &amp;lt;개정 2019.1.31, 2022.10.18&amp;gt;&lt;br&gt;▶  1. 강도는 지게차의 최대하중의 2배 값(4톤&lt;strong&gt;을 넘는 값에 대해서는 4&lt;/strong&gt;톤으로 한다)의 등분포정하중(等分布靜荷重)에 견딜 수 있을 것&lt;br&gt;▶  2. &lt;strong&gt;상부틀의 각 개구의 폭 또는 길이가&lt;/strong&gt; 16센티미터 미만일 것&lt;br&gt; 3. 운전자가 앉아서 조작하거나 서서 조작하는 지게차의 헤드가드는 한국산업표준에서 정하는 높이 기준 이상일 것&lt;br&gt; 4. 삭제&amp;lt;2019.1.31&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8427,7 @@
       </c>
       <c r="AI57" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제223조 — 운전 중 위험 방지&lt;/strong&gt;&lt;br&gt;세 조치가 모두 &lt;strong&gt;「남이 모르고 켜지 못하게」&lt;/strong&gt; 하는 것이다 — &lt;strong&gt;표시하고 · 잠그고 · 열쇠를 따로 둔다&lt;/strong&gt;. 보기 ②만 그 반대다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작업자 말고는 스위치를 만질 수 없게&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C223%EC%A1%B0" target="_blank"&gt;제223조(운전 중 위험 방지)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;제223조(운전 중 위험 방지) 사업주는 로봇의 운전(제222조에 따른 교시 등을 위한 로봇의 운전과 제224조 단서에 따른 로봇의 운전은 제외한다)으로 인하여 근로자에게 발생할 수 있는 부상 등의 위험을 방지하기 위하여 높이 1.8미터 이상의 울타리(로봇의 가동범위 등을 고려하여 높이로 인한 위험성이 없는 경우에는 높이를 그 이하로 조절할 수 있다)를 설치해야 하며, 컨베이어 시스템의 설치 등으로 울타리를 설치할 수 없는 일부 구간에 대해서는 안전매트 또는 광전자식 방호장치 등 감응형 방호장치를 설치해야 한다. 다만, 고용노동부장관이 해당 로봇의 안전기준이 한국산업표준에서 정하고 있는 안전기준 또는 국제적으로 통용되는 안전기준에 부합한다고 인정하는 경우에는 본문에 따른 조치를 하지 않을 수 있다. &amp;lt;개정 2016.4.7, 2018.8.14, 2022.10.18, 2024.6.28&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제223조 — 운전 중 위험 방지&lt;/strong&gt;&lt;br&gt;세 조치가 모두 &lt;strong&gt;「남이 모르고 켜지 못하게」&lt;/strong&gt;하는 것이다 — &lt;strong&gt;표시하고 · 잠그고 · 열쇠를 따로 둔다&lt;/strong&gt;. 보기 ②만 그 반대다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작업자 말고는 스위치를 만질 수 없게&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C223%EC%A1%B0" target="_blank"&gt;제223조(운전 중 위험 방지)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;제223조(운전 중 위험 방지) 사업주는 로봇의 운전(제222조에 따른 교시 등을 위한 로봇의 운전과 제224조 단서에 따른 로봇의 운전은 제외한다)으로 인하여 근로자에게 발생할 수 있는 부상 등의 위험을 방지하기 위하여 높이 1.8미터 이상의 울타리(로봇의 가동범위 등을 고려하여 높이로 인한 위험성이 없는 경우에는 높이를 그 이하로 조절할 수 있다)를 설치해야 하며, 컨베이어 시스템의 설치 등으로 울타리를 설치할 수 없는 일부 구간에 대해서는 안전매트 또는 광전자식 방호장치 등 감응형 방호장치를 설치해야 한다. 다만, 고용노동부장관이 해당 로봇의 안전기준이 한국산업표준에서 정하고 있는 안전기준 또는 국제적으로 통용되는 안전기준에 부합한다고 인정하는 경우에는 본문에 따른 조치를 하지 않을 수 있다. &amp;lt;개정 2016.4.7, 2018.8.14, 2022.10.18, 2024.6.28&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8556,7 @@
       </c>
       <c r="AI58" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;자분탐상검사(MT)의 적용 한계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;자분탐상은 자력선이 새는 자리에 쇳가루가 모이는 원리&lt;/strong&gt;라 &lt;strong&gt;자석에 붙는 재료(강자성체)&lt;/strong&gt; 라야 한다. &lt;strong&gt;오스테나이트계 스테인리스강(304 · 316 등)은 자석에 붙지 않는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비자성체에는 자분탐상을 못 쓴다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;자분탐상검사(MT)의 적용 한계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;자분탐상은 자력선이 새는 자리에 쇳가루가 모이는 원리&lt;/strong&gt;라 &lt;strong&gt;자석에 붙는 재료(강자성체)&lt;/strong&gt;라야 한다. &lt;strong&gt;오스테나이트계 스테인리스강(304 · 316 등)은 자석에 붙지 않는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비자성체에는 자분탐상을 못 쓴다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8680,7 @@
       </c>
       <c r="AH59" s="32" t="inlineStr">
         <is>
-          <t>② 30 [cm] 라는 기준은 없다.&lt;br&gt;③ 35 [cm] 도 없다.&lt;br&gt;④ 40 [cm] 도 없다.</t>
+          <t>② 30 [cm]라는 기준은 없다.&lt;br&gt;③ 35 [cm] 도 없다.&lt;br&gt;④ 40 [cm] 도 없다.</t>
         </is>
       </c>
       <c r="AI59" s="32" t="inlineStr">
@@ -8800,12 +8804,12 @@
       </c>
       <c r="AG60" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;앞바퀴를 받침점으로 한 모멘트의 균형&lt;/strong&gt;을 잡는다. $W \times a \le G \times b$ 에서 $W \times 2 \le 30 \times 3$ 이므로 $W \le 45$ [kN] 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차의 안정조건&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이 문항에서는&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하물의 무게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;W&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;구하는 값&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;앞바퀴에서 하물 중심까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;a&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [m]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;차량의 무게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;G&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [kN]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;앞바퀴에서 차량 중심까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;b&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3 [m]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안정조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W a \le G b$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;45 [kN] 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;앞바퀴를 받침점으로 한 모멘트의 균형&lt;/strong&gt;을 잡는다. $W \times a \le G \times b$에서 $W \times 2 \le 30 \times 3$이므로 $W \le 45$ [kN]이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차의 안정조건&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이 문항에서는&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하물의 무게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;W&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;구하는 값&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;앞바퀴에서 하물 중심까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;a&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [m]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;차량의 무게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;G&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [kN]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;앞바퀴에서 차량 중심까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;b&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3 [m]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안정조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W a \le G b$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;45 [kN] 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH60" s="32" t="inlineStr">
         <is>
-          <t>① 15 [kN] 은 계산과 맞지 않는다.&lt;br&gt;② 25 [kN] 도 맞지 않는다.&lt;br&gt;③ 35 [kN] 도 맞지 않는다.</t>
+          <t>① 15 [kN]은 계산과 맞지 않는다.&lt;br&gt;② 25 [kN] 도 맞지 않는다.&lt;br&gt;③ 35 [kN] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI60" s="32" t="inlineStr">
@@ -9063,7 +9067,7 @@
       </c>
       <c r="AH62" s="32" t="inlineStr">
         <is>
-          <t>① 「직경의 1/3」이 아니라 「원주의 1/3」이다.&lt;br&gt;② 30 [m/min] 이상이면 원주의 1/2.5 이내다.&lt;br&gt;④ 30 [m/min] 이상일 때는 1/3 이 아니라 1/2.5 다.</t>
+          <t>① 「직경의 1/3」이 아니라 「원주의 1/3」이다.&lt;br&gt;② 30 [m/min] 이상이면 원주의 1/2.5 이내다.&lt;br&gt;④ 30 [m/min] 이상일 때는 1/3이 아니라 1/2.5다.</t>
         </is>
       </c>
       <c r="AI62" s="32" t="inlineStr">
@@ -9197,7 +9201,7 @@
       </c>
       <c r="AI63" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;교류아크용접기의 배선&lt;/strong&gt;&lt;br&gt;용접기 2차측은 &lt;strong&gt;늘 끌려다니며 구부러지므로 부드럽고 튼튼한 캡타이어 케이블&lt;/strong&gt; 이라야 한다. &lt;strong&gt;비닐절연전선은 고정 배선용&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;2차측은 용접용 캡타이어 케이블&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;교류아크용접기의 배선&lt;/strong&gt;&lt;br&gt;용접기 2차측은 &lt;strong&gt;늘 끌려다니며 구부러지므로 부드럽고 튼튼한 캡타이어 케이블&lt;/strong&gt;이라야 한다. &lt;strong&gt;비닐절연전선은 고정 배선용&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;2차측은 용접용 캡타이어 케이블&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9583,7 @@
       </c>
       <c r="AH66" s="32" t="inlineStr">
         <is>
-          <t>① 15 [mA] 는 물기 있는 장소의 기준이며 시간도 0.1초가 아니다.&lt;br&gt;③ 50 [mA] 는 심실세동전류 영역이라 감도전류가 될 수 없다.&lt;br&gt;④ 100 [mA] 도 마찬가지다.</t>
+          <t>① 15 [mA]는 물기 있는 장소의 기준이며 시간도 0.1초가 아니다.&lt;br&gt;③ 50 [mA]는 심실세동전류 영역이라 감도전류가 될 수 없다.&lt;br&gt;④ 100 [mA] 도 마찬가지다.</t>
         </is>
       </c>
       <c r="AI66" s="32" t="inlineStr">
@@ -9703,17 +9707,17 @@
       </c>
       <c r="AG67" s="32" t="inlineStr">
         <is>
-          <t>$W = I^{2} R T = ( 165 \times 10^{-3} )^{2} \times 500 \times 1 \fallingdotseq 13.6$ [J] 이고, &lt;strong&gt;통전시간을 0.5 ~ 1.3초 범위로 잡으면 약 6.5 ~ 17.0 [J]&lt;/strong&gt;이 된다.</t>
+          <t>$W = I^{2} R T = ( 165 \times 10^{-3} )^{2} \times 500 \times 1 \fallingdotseq 13.6$ [J]이고, &lt;strong&gt;통전시간을 0.5 ~ 1.3초 범위로 잡으면 약 6.5 ~ 17.0 [J]&lt;/strong&gt;이 된다.</t>
         </is>
       </c>
       <c r="AH67" s="32" t="inlineStr">
         <is>
-          <t>② 15.0 ~ 25.5 [J] 는 범위가 위로 치우쳐 있다.&lt;br&gt;③ 20.5 ~ 30.5 [J] 도 그렇다.&lt;br&gt;④ 31.5 ~ 38.5 [J] 는 저항 1,000 [Ω] 쪽에 가깝다.</t>
+          <t>② 15.0 ~ 25.5 [J]는 범위가 위로 치우쳐 있다.&lt;br&gt;③ 20.5 ~ 30.5 [J] 도 그렇다.&lt;br&gt;④ 31.5 ~ 38.5 [J]는 저항 1,000 [Ω] 쪽에 가깝다.</t>
         </is>
       </c>
       <c r="AI67" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;심실세동 한계에너지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;500 [Ω] 에서 13.6 [J]&lt;/strong&gt;이라는 값을 가운데에 두고 보면 &lt;strong&gt;6.5 ~ 17.0 [J]&lt;/strong&gt;이 그것을 품는 유일한 범위다. &lt;strong&gt;다른 보기는 모두 13.6 을 벗어난다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;500 [Ω] 이면 13.6 [J]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;심실세동 한계에너지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;500 [Ω]에서 13.6 [J]&lt;/strong&gt;이라는 값을 가운데에 두고 보면 &lt;strong&gt;6.5 ~ 17.0 [J]&lt;/strong&gt;이 그것을 품는 유일한 범위다. &lt;strong&gt;다른 보기는 모두 13.6을 벗어난다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;500 [Ω] 이면 13.6 [J]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9832,7 +9836,7 @@
       </c>
       <c r="AG68" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;보호용구 없이 맨손으로 감전자를 잡으면 구조자까지 감전&lt;/strong&gt; 된다. &lt;strong&gt;먼저 전원을 끊거나 절연물로 떼어 놓아야&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;감전자 구출의 순서&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;순서&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 하나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전원을 끊는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 먼저&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;끊을 수 없으면 절연물(마른 나무·고무장갑)로 떼어 놓는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;맨손 금지&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전한 곳으로 옮기고 의식·호흡·맥박을 살핀다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;심폐소생술을 실시한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1인 30 : 2 · 2인 15 : 2&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;보호용구 없이 맨손으로 감전자를 잡으면 구조자까지 감전&lt;/strong&gt;된다. &lt;strong&gt;먼저 전원을 끊거나 절연물로 떼어 놓아야&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;감전자 구출의 순서&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;순서&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 하나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전원을 끊는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 먼저&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;끊을 수 없으면 절연물(마른 나무·고무장갑)로 떼어 놓는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;맨손 금지&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전한 곳으로 옮기고 의식·호흡·맥박을 살핀다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;심폐소생술을 실시한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1인 30 : 2 · 2인 15 : 2&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH68" s="32" t="inlineStr">
@@ -10225,7 +10229,7 @@
       </c>
       <c r="AI71" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방폭의 기본 개념&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;유입은 기름 속에 담가 불꽃을 가두는 것&lt;/strong&gt;이라 「격리」쪽이다. &lt;strong&gt;「위험분위기 해소」는 깨끗한 공기를 밀어 넣어 가스를 몰아내는 압력 방폭구조&lt;/strong&gt; 뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;위험분위기 해소는 압력 방폭구조&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방폭의 기본 개념&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;유입은 기름 속에 담가 불꽃을 가두는 것&lt;/strong&gt;이라 「격리」쪽이다. &lt;strong&gt;「위험분위기 해소」는 깨끗한 공기를 밀어 넣어 가스를 몰아내는 압력 방폭구조&lt;/strong&gt;뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;위험분위기 해소는 압력 방폭구조&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10607,12 +10611,12 @@
       </c>
       <c r="AH74" s="32" t="inlineStr">
         <is>
-          <t>① $10^{-3}$ [C] 은 지나치게 큰 값이다.&lt;br&gt;② $10^{-5}$ [C] 도 크다.&lt;br&gt;④ $10^{-9}$ [C] 은 느끼지 못할 만큼 작다.</t>
+          <t>① $10^{-3}$ [C]은 지나치게 큰 값이다.&lt;br&gt;② $10^{-5}$ [C] 도 크다.&lt;br&gt;④ $10^{-9}$ [C]은 느끼지 못할 만큼 작다.</t>
         </is>
       </c>
       <c r="AI74" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;인체 대전과 정전기 통증&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;인체의 정전용량은 약 100 [pF]&lt;/strong&gt;이므로 $Q = CV$ 에서 $2.5 \times 10^{-7}$&lt;strong&gt; [C] 은 약 2,500 [V]&lt;/strong&gt;에 해당한다. &lt;strong&gt;사람이 정전기를 느끼기 시작하는 것이 대략 3,000 [V]&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $2 \sim 3 \times 10^{-7}$ [C].&lt;/p&gt;</t>
+          <t>&lt;strong&gt;인체 대전과 정전기 통증&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;인체의 정전용량은 약 100 [pF]&lt;/strong&gt;이므로 $Q = CV$에서 $2.5 \times 10^{-7}$&lt;strong&gt; [C]은 약 2,500 [V]&lt;/strong&gt;에 해당한다. &lt;strong&gt;사람이 정전기를 느끼기 시작하는 것이 대략 3,000 [V]&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $2 \sim 3 \times 10^{-7}$ [C].&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10736,12 +10740,12 @@
       </c>
       <c r="AH75" s="32" t="inlineStr">
         <is>
-          <t>① 100 [mA] 는 계산과 맞지 않는다.&lt;br&gt;③ 1,000 [mA] 는 자릿수가 어긋난다.&lt;br&gt;④ 1,500 [mA] 도 그렇다.</t>
+          <t>① 100 [mA]는 계산과 맞지 않는다.&lt;br&gt;③ 1,000 [mA]는 자릿수가 어긋난다.&lt;br&gt;④ 1,500 [mA] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI75" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;누설전류의 허용값&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1/2,000&lt;/strong&gt;이라는 비율만 기억하면 한 줄로 끝난다. &lt;strong&gt;[A] 로 나눈 뒤 1,000 을 곱해 [mA] 로&lt;/strong&gt; 바꾸는 것을 놓치지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누설전류는 최대공급전류의 1/2,000&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;누설전류의 허용값&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1/2,000&lt;/strong&gt;이라는 비율만 기억하면 한 줄로 끝난다. &lt;strong&gt;[A]로 나눈 뒤 1,000을 곱해 [mA]로&lt;/strong&gt; 바꾸는 것을 놓치지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누설전류는 최대공급전류의 1/2,000&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11257,7 +11261,7 @@
       </c>
       <c r="AI79" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;접지저항의 저감&lt;/strong&gt;&lt;br&gt;접지저항의 대부분은 &lt;strong&gt;접지극 둘레 흙의 저항&lt;/strong&gt;이다. &lt;strong&gt;닿는 면적을 넓히거나(크게 · 길게 · 여러 개) 흙 자체를 잘 통하게(저감제)&lt;/strong&gt; 하면 낮아진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;접지극은 크게&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;접지저항의 저감&lt;/strong&gt;&lt;br&gt;접지저항의 대부분은 &lt;strong&gt;접지극 둘레 흙의 저항&lt;/strong&gt;이다. &lt;strong&gt;닿는 면적을 넓히거나(크게 · 길게 · 여러 개) 흙 자체를 잘 통하게(저감제)&lt;/strong&gt;하면 낮아진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;접지극은 크게&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11634,17 +11638,17 @@
       </c>
       <c r="AG82" s="32" t="inlineStr">
         <is>
-          <t>관 내경 25 [mm] 의 제한유속은 &lt;strong&gt;4.9 [m/s]&lt;/strong&gt;다. 6.5 [m/s] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;관 내경별 제한유속 (저항률 $10^{10}$ [Ω·cm] 이상)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;관 내경 [mm]&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;제한유속 [m/s]&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;8.0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;25&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4.9&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6.5 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;100&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;200&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.8&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;400&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;600&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>관 내경 25 [mm]의 제한유속은 &lt;strong&gt;4.9 [m/s]&lt;/strong&gt;다. 6.5 [m/s]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;관 내경별 제한유속 (저항률 $10^{10}$ [Ω·cm] 이상)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;관 내경 [mm]&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;제한유속 [m/s]&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;8.0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;25&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4.9&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6.5가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;100&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;200&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.8&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;400&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;600&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH82" s="32" t="inlineStr">
         <is>
-          <t>② 50 [mm] 에 3.5 [m/s] 는 맞다.&lt;br&gt;③ 100 [mm] 에 2.5 [m/s] 도 맞다.&lt;br&gt;④ 200 [mm] 에 1.8 [m/s] 도 맞다.</t>
+          <t>② 50 [mm]에 3.5 [m/s]는 맞다.&lt;br&gt;③ 100 [mm]에 2.5 [m/s] 도 맞다.&lt;br&gt;④ 200 [mm]에 1.8 [m/s] 도 맞다.</t>
         </is>
       </c>
       <c r="AI82" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;배관 내경별 유속 제한&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;관이 굵을수록 제한유속이 낮아진다&lt;/strong&gt; — &lt;strong&gt;굵을수록 한꺼번에 많은 양이 흘러 전하가 많이 생기기&lt;/strong&gt; 때문이다. $v^{2} d \le 0.64$라는 관계에서 나온 값들이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;25 [mm] 는 4.9 [m/s]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;배관 내경별 유속 제한&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;관이 굵을수록 제한유속이 낮아진다&lt;/strong&gt; — &lt;strong&gt;굵을수록 한꺼번에 많은 양이 흘러 전하가 많이 생기기&lt;/strong&gt; 때문이다. $v^{2} d \le 0.64$라는 관계에서 나온 값들이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;25 [mm]는 4.9 [m/s]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11765,7 +11769,7 @@
       </c>
       <c r="AI83" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;공비증류(azeotropic distillation)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;에탄올과 물은 95.6 [%] 에서 공비점&lt;/strong&gt;이 있어 &lt;strong&gt;보통 증류로는 그 이상 진하게 만들 수&lt;/strong&gt; 없다. &lt;strong&gt;벤젠을 넣어 삼성분 공비혼합물을 만들면&lt;/strong&gt; 물을 먼저 뽑아낼 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;제3의 물질로 공비혼합물을 만들면 공비증류&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;공비증류(azeotropic distillation)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;에탄올과 물은 95.6 [%]에서 공비점&lt;/strong&gt;이 있어 &lt;strong&gt;보통 증류로는 그 이상 진하게 만들 수&lt;/strong&gt; 없다. &lt;strong&gt;벤젠을 넣어 삼성분 공비혼합물을 만들면&lt;/strong&gt; 물을 먼저 뽑아낼 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;제3의 물질로 공비혼합물을 만들면 공비증류&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12010,7 +12014,7 @@
       </c>
       <c r="AH85" s="32" t="inlineStr">
         <is>
-          <t>② 메탄이 가장 간단한 탄화수소이며 온실효과가 있는 것은 맞다.&lt;br&gt;③ 수소가 물에 잘 녹지 않고 온도가 오르면 반응성이 커지는 것도 맞다.&lt;br&gt;④ 프로판의 폭발범위 2.1 ~ 9.5 [%] 와 공기보다 무거운 것도 맞다.</t>
+          <t>② 메탄이 가장 간단한 탄화수소이며 온실효과가 있는 것은 맞다.&lt;br&gt;③ 수소가 물에 잘 녹지 않고 온도가 오르면 반응성이 커지는 것도 맞다.&lt;br&gt;④ 프로판의 폭발범위 2.1 ~ 9.5 [%]와 공기보다 무거운 것도 맞다.</t>
         </is>
       </c>
       <c r="AI85" s="32" t="inlineStr">
@@ -12138,17 +12142,17 @@
       </c>
       <c r="AG86" s="32" t="inlineStr">
         <is>
-          <t>$H = \dfrac{U - L}{L}$ 로 셈한다. $A = \dfrac{9.5 - 2.1}{2.1} \fallingdotseq 3.52$, $B = \dfrac{8.4 - 1.8}{1.8} \fallingdotseq 3.67$, $C = \dfrac{15 - 5}{5} = 2.0$, $D = \dfrac{13 - 2.6}{2.6} = 4.0$ 이므로 &lt;strong&gt;D 가 가장 크다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;위험도의 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상한계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;하한계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;위험도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;A&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;9.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.52&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;프로판&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;8.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.8&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.67&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;부탄&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;C&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;15.0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5.0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.00&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;메탄&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;D&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;13&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4.00&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 크다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$H = \dfrac{U - L}{L}$로 셈한다. $A = \dfrac{9.5 - 2.1}{2.1} \fallingdotseq 3.52$, $B = \dfrac{8.4 - 1.8}{1.8} \fallingdotseq 3.67$, $C = \dfrac{15 - 5}{5} = 2.0$, $D = \dfrac{13 - 2.6}{2.6} = 4.0$이므로 &lt;strong&gt;D가 가장 크다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;위험도의 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상한계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;하한계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;위험도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;A&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;9.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.52&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;프로판&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;8.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.8&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.67&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;부탄&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;C&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;15.0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5.0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.00&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;메탄&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;D&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;13&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4.00&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 크다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH86" s="32" t="inlineStr">
         <is>
-          <t>① A 의 위험도는 3.52 다.&lt;br&gt;② B 는 3.67 이다.&lt;br&gt;③ C 는 2.0 으로 가장 작다.</t>
+          <t>① A의 위험도는 3.52다.&lt;br&gt;② B는 3.67이다.&lt;br&gt;③ C는 2.0으로 가장 작다.</t>
         </is>
       </c>
       <c r="AI86" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;위험도(H)&lt;/strong&gt;&lt;br&gt;$H = \dfrac{U - L}{L}$ 다. &lt;strong&gt;하한계가 작을수록, 범위가 넓을수록 위험도가 크다&lt;/strong&gt;. &lt;strong&gt;분모가 하한계&lt;/strong&gt;라는 점이 갈림길이라, &lt;strong&gt;범위가 가장 넓은 C(10)가 오히려 가장 낮다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $H = ( U - L ) \div L$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;위험도(H)&lt;/strong&gt;&lt;br&gt;$H = \dfrac{U - L}{L}$다. &lt;strong&gt;하한계가 작을수록, 범위가 넓을수록 위험도가 크다&lt;/strong&gt;. &lt;strong&gt;분모가 하한계&lt;/strong&gt;라는 점이 갈림길이라, &lt;strong&gt;범위가 가장 넓은 C(10)가 오히려 가장 낮다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $H = ( U - L ) \div L$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12267,7 +12271,7 @@
       </c>
       <c r="AG87" s="32" t="inlineStr">
         <is>
-          <t>니트로셀룰로오스는 &lt;strong&gt;마르면 자연발화&lt;/strong&gt; 한다. &lt;strong&gt;물이나 알코올로 적셔서 저장&lt;/strong&gt; 해야 한다. &lt;strong&gt;물과 반응해 폭발하는 것이 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;니트로셀룰로오스(질화면)의 취급&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;내용&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;분류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제5류 자기반응성 물질&lt;/u&gt; (질산에스테르류)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;저장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물이나 알코올(에탄올·메탄올)로 적셔서&lt;/u&gt; — 건조는 금물&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;건조하면 분해열로 자연발화&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;소화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다량의 물로 냉각소화&lt;/u&gt; — 질식·억제소화는 듣지 않는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주의&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;충격과 마찰을 피할 것&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>니트로셀룰로오스는 &lt;strong&gt;마르면 자연발화&lt;/strong&gt;한다. &lt;strong&gt;물이나 알코올로 적셔서 저장&lt;/strong&gt;해야 한다. &lt;strong&gt;물과 반응해 폭발하는 것이 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;니트로셀룰로오스(질화면)의 취급&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;내용&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;분류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제5류 자기반응성 물질&lt;/u&gt; (질산에스테르류)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;저장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물이나 알코올(에탄올·메탄올)로 적셔서&lt;/u&gt; — 건조는 금물&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;건조하면 분해열로 자연발화&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;소화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다량의 물로 냉각소화&lt;/u&gt; — 질식·억제소화는 듣지 않는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주의&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;충격과 마찰을 피할 것&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH87" s="32" t="inlineStr">
@@ -12400,17 +12404,17 @@
       </c>
       <c r="AG88" s="32" t="inlineStr">
         <is>
-          <t>반응식에서 &lt;strong&gt;산소 5몰&lt;/strong&gt;이 필요하므로 $C_{\mathrm{st}} = \dfrac{100}{1 + 4.773 \times 5} = \dfrac{100}{24.865} \fallingdotseq 4.02$ [vol%] 다. 따라서 $\mathrm{LFL} = 0.55 \times 4.02 \fallingdotseq 2.21$ [vol%] 다.</t>
+          <t>반응식에서 &lt;strong&gt;산소 5몰&lt;/strong&gt;이 필요하므로 $C_{\mathrm{st}} = \dfrac{100}{1 + 4.773 \times 5} = \dfrac{100}{24.865} \fallingdotseq 4.02$ [vol%]다. 따라서 $\mathrm{LFL} = 0.55 \times 4.02 \fallingdotseq 2.21$ [vol%]다.</t>
         </is>
       </c>
       <c r="AH88" s="32" t="inlineStr">
         <is>
-          <t>② 4.03 [vol%] 는 화학양론조성 $C_{\mathrm{st}}$ 값이다.&lt;br&gt;③ 4.44 [vol%] 도 맞지 않는다.&lt;br&gt;④ 8.06 [vol%] 는 $C_{\mathrm{st}}$ 의 두 배다.</t>
+          <t>② 4.03 [vol%]는 화학양론조성 $C_{\mathrm{st}}$ 값이다.&lt;br&gt;③ 4.44 [vol%] 도 맞지 않는다.&lt;br&gt;④ 8.06 [vol%]는 $C_{\mathrm{st}}$의 두 배다.</t>
         </is>
       </c>
       <c r="AI88" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Jones 식과 화학양론조성&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;반응식에 산소 계수가 이미 적혀 있으면 &lt;/strong&gt;$n + m / 4$&lt;strong&gt; 를 따로 구할 필요가 없다&lt;/strong&gt; — &lt;strong&gt;그 계수를 그대로 4.773 에 곱하면&lt;/strong&gt; 된다. &lt;strong&gt;상한계는 &lt;/strong&gt;$\mathrm{UFL} = 3.50 \times C_{\mathrm{st}}$다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;LFL = 0.55 × &lt;/u&gt;$C_{\mathrm{st}}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;Jones 식과 화학양론조성&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;반응식에 산소 계수가 이미 적혀 있으면 &lt;/strong&gt;$n + m / 4$&lt;strong&gt;를 따로 구할 필요가 없다&lt;/strong&gt; — &lt;strong&gt;그 계수를 그대로 4.773에 곱하면&lt;/strong&gt; 된다. &lt;strong&gt;상한계는 &lt;/strong&gt;$\mathrm{UFL} = 3.50 \times C_{\mathrm{st}}$다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;LFL = 0.55 × &lt;/u&gt;$C_{\mathrm{st}}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12662,12 +12666,12 @@
       </c>
       <c r="AG90" s="32" t="inlineStr">
         <is>
-          <t>$H = \dfrac{U - L}{L}$ 로 셈하면 프로판 2.96, 부탄 3.67, 벤젠 $\dfrac{6.7 - 1.4}{1.4} \fallingdotseq 3.79$, 가솔린 3.43 이므로 &lt;strong&gt;벤젠이 가장 크다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;위험도의 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;UFL&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;LFL&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;위험도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;프로판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;9.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.96&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부탄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;8.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.8&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.67&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;벤젠&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6.7&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.79&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 크다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가솔린&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6.2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.43&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$H = \dfrac{U - L}{L}$로 셈하면 프로판 2.96, 부탄 3.67, 벤젠 $\dfrac{6.7 - 1.4}{1.4} \fallingdotseq 3.79$, 가솔린 3.43이므로 &lt;strong&gt;벤젠이 가장 크다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;위험도의 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;UFL&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;LFL&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;위험도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;프로판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;9.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.96&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부탄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;8.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.8&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.67&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;벤젠&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6.7&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.79&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 크다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가솔린&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6.2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.43&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH90" s="32" t="inlineStr">
         <is>
-          <t>① 프로판의 위험도는 2.96 으로 가장 작다.&lt;br&gt;② 부탄은 3.67 이다.&lt;br&gt;④ 가솔린은 3.43 이다.</t>
+          <t>① 프로판의 위험도는 2.96으로 가장 작다.&lt;br&gt;② 부탄은 3.67이다.&lt;br&gt;④ 가솔린은 3.43이다.</t>
         </is>
       </c>
       <c r="AI90" s="32" t="inlineStr">
@@ -13049,17 +13053,17 @@
       </c>
       <c r="AG93" s="32" t="inlineStr">
         <is>
-          <t>분진은 &lt;strong&gt;[mg/㎥]&lt;/strong&gt;로 나타낸다. &lt;strong&gt;[ppm] 은 기체(가스·증기)의 단위&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;노출기준의 표시단위&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가스 · 증기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[ppm] 또는 [mg/㎥]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;부피 비율 또는 질량 농도&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;분진(먼지)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[mg/㎥]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[ppm] 을 쓸 수 없다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;석면 · 섬유&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[개/㎤]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;개수 농도&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고온&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;습구흑구온도지수(WBGT) [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>분진은 &lt;strong&gt;[mg/㎥]&lt;/strong&gt;로 나타낸다. &lt;strong&gt;[ppm]은 기체(가스·증기)의 단위&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;노출기준의 표시단위&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가스 · 증기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[ppm] 또는 [mg/㎥]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;부피 비율 또는 질량 농도&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;분진(먼지)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[mg/㎥]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[ppm]을 쓸 수 없다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;석면 · 섬유&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[개/㎤]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;개수 농도&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고온&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;습구흑구온도지수(WBGT) [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH93" s="32" t="inlineStr">
         <is>
-          <t>② 증기를 [ppm] 으로 나타내는 것은 맞다.&lt;br&gt;③ 가스를 [mg/㎥] 로 나타내는 것도 맞다.&lt;br&gt;④ 고온을 습구흑구온도지수로 나타내는 것도 맞다.</t>
+          <t>② 증기를 [ppm]으로 나타내는 것은 맞다.&lt;br&gt;③ 가스를 [mg/㎥]로 나타내는 것도 맞다.&lt;br&gt;④ 고온을 습구흑구온도지수로 나타내는 것도 맞다.</t>
         </is>
       </c>
       <c r="AI93" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;노출기준의 표시단위&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;[ppm] 은 「부피 백만분율」&lt;/strong&gt;이라 &lt;strong&gt;기체끼리만 견줄 수&lt;/strong&gt; 있다. &lt;strong&gt;고체 알갱이인 분진은 부피를 셀 수 없으므로 무게(mg)로&lt;/strong&gt; 나타낸다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;분진은 [mg/㎥]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;노출기준의 표시단위&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;[ppm]은 「부피 백만분율」&lt;/strong&gt;이라 &lt;strong&gt;기체끼리만 견줄 수&lt;/strong&gt; 있다. &lt;strong&gt;고체 알갱이인 분진은 부피를 셀 수 없으므로 무게(mg)로&lt;/strong&gt; 나타낸다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;분진은 [mg/㎥]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13178,7 +13182,7 @@
       </c>
       <c r="AG94" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;주요 구입 및 폐기처&lt;/strong&gt;는 MSDS 의 항목이 아니다. &lt;strong&gt;거래처는 물질의 성질과 무관&lt;/strong&gt; 하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;MSDS 의 16개 항목&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1. 화학제품과 회사에 관한 정보&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2. 유해성·위험성&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3. 구성성분의 명칭 및 함유량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4. 응급조치 요령&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5. 폭발·화재 시 대처방법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6. 누출 사고 시 대처방법&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;7. 취급 및 저장방법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;8. 노출방지 및 개인보호구&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;9. 물리화학적 특성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10. 안정성 및 반응성&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;11. 독성에 관한 정보&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;12. 환경에 미치는 영향&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;13. 폐기 시 주의사항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;14. 운송에 필요한 정보&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;15. 법적 규제현황&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;16. 그 밖의 참고사항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;주요 구입 및 폐기처&lt;/strong&gt;는 MSDS의 항목이 아니다. &lt;strong&gt;거래처는 물질의 성질과 무관&lt;/strong&gt;하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;MSDS의 16개 항목&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1. 화학제품과 회사에 관한 정보&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2. 유해성·위험성&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3. 구성성분의 명칭 및 함유량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4. 응급조치 요령&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5. 폭발·화재 시 대처방법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6. 누출 사고 시 대처방법&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;7. 취급 및 저장방법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;8. 노출방지 및 개인보호구&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;9. 물리화학적 특성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10. 안정성 및 반응성&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;11. 독성에 관한 정보&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;12. 환경에 미치는 영향&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;13. 폐기 시 주의사항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;14. 운송에 필요한 정보&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;15. 법적 규제현황&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;16. 그 밖의 참고사항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH94" s="32" t="inlineStr">
@@ -13317,7 +13321,7 @@
       </c>
       <c r="AI95" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;화재의 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;A 일반 백색 · B 유류 황색 · C 전기 청색 · D 금속 무색&lt;/strong&gt; 네 짝으로 외운다. &lt;strong&gt;A급은 재를 남기는 화재&lt;/strong&gt;라 하여 &lt;strong&gt;물로 냉각소화&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;종이 · 목재 · 섬유는 A급&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;화재의 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;A 일반 백색 · B 유류 황색 · C 전기 청색 · D 금속 무색&lt;/strong&gt; 네 짝으로 외운다. &lt;strong&gt;A급은 재를 남기는 화재&lt;/strong&gt;라 하여 &lt;strong&gt;물로 냉각소화&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;종이 · 목재 · 섬유는 A급&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13436,7 +13440,7 @@
       </c>
       <c r="AG96" s="32" t="inlineStr">
         <is>
-          <t>분말은 &lt;strong&gt;흡습력이 크고 금속을 부식&lt;/strong&gt; 시킨다. 그래서 &lt;strong&gt;습기를 피해 보관&lt;/strong&gt; 해야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;분말 소화설비의 장단점&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장점&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단점&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;내용&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;소화능력이 뛰어나고 소화시간이 짧다 · 기구가 간단하고 유지관리가 쉽다 · 온도 변화에 약제가 변질되지 않는다 · 전기 부도체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;흡습력이 커서 굳는다 · 금속을 부식시킨다 · 잔재가 남아 정밀기기에 쓸 수 없다 · 재발화 우려&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>분말은 &lt;strong&gt;흡습력이 크고 금속을 부식&lt;/strong&gt; 시킨다. 그래서 &lt;strong&gt;습기를 피해 보관&lt;/strong&gt;해야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;분말 소화설비의 장단점&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장점&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단점&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;내용&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;소화능력이 뛰어나고 소화시간이 짧다 · 기구가 간단하고 유지관리가 쉽다 · 온도 변화에 약제가 변질되지 않는다 · 전기 부도체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;흡습력이 커서 굳는다 · 금속을 부식시킨다 · 잔재가 남아 정밀기기에 쓸 수 없다 · 재발화 우려&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH96" s="32" t="inlineStr">
@@ -13446,7 +13450,7 @@
       </c>
       <c r="AI96" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;분말 소화설비&lt;/strong&gt;&lt;br&gt;분말은 &lt;strong&gt;억제(부촉매)소화로 불은 잘 끄지만 뒤가 지저분&lt;/strong&gt; 하다. &lt;strong&gt;굳고 · 녹슬고 · 남는다&lt;/strong&gt;는 세 가지가 단점이다. &lt;strong&gt;정밀기기에는 이산화탄소&lt;/strong&gt;를 쓴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;분말은 흡습력이 크고 부식시킨다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;분말 소화설비&lt;/strong&gt;&lt;br&gt;분말은 &lt;strong&gt;억제(부촉매)소화로 불은 잘 끄지만 뒤가 지저분&lt;/strong&gt;하다. &lt;strong&gt;굳고 · 녹슬고 · 남는다&lt;/strong&gt;는 세 가지가 단점이다. &lt;strong&gt;정밀기기에는 이산화탄소&lt;/strong&gt;를 쓴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;분말은 흡습력이 크고 부식시킨다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13699,7 +13703,7 @@
       </c>
       <c r="AH98" s="32" t="inlineStr">
         <is>
-          <t>① 5 [m] 는 기준에 못 미친다.&lt;br&gt;③ 15 [m] 라는 기준은 없다.&lt;br&gt;④ 20 [m] 는 플레어스택·저장탱크·사무실 등의 기준이다.</t>
+          <t>① 5 [m]는 기준에 못 미친다.&lt;br&gt;③ 15 [m]라는 기준은 없다.&lt;br&gt;④ 20 [m]는 플레어스택·저장탱크·사무실 등의 기준이다.</t>
         </is>
       </c>
       <c r="AI98" s="32" t="inlineStr">
@@ -14081,7 +14085,7 @@
       </c>
       <c r="AG101" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;밸브류&lt;/strong&gt;는 압력계 설치 대상이 아니다. &lt;strong&gt;흐름을 여닫는 부속&lt;/strong&gt; 일 뿐이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;압력계를 설치해야 하는 설비 (운전압력 3 [psig] 이상)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;설비&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반응기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;탑조류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;드럼&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;열교환기&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;회전기계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;배관&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;밸브류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대상이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;밸브류&lt;/strong&gt;는 압력계 설치 대상이 아니다. &lt;strong&gt;흐름을 여닫는 부속&lt;/strong&gt;일 뿐이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;압력계를 설치해야 하는 설비 (운전압력 3 [psig] 이상)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;설비&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반응기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;탑조류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;드럼&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;열교환기&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;회전기계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;배관&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;밸브류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대상이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH101" s="32" t="inlineStr">
@@ -14349,7 +14353,7 @@
       </c>
       <c r="AI103" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제23조 — 가설통로의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;30 과 15&lt;/strong&gt;를 짝으로 잡는다 — &lt;strong&gt;경사는 30° 까지 허용하되, 15° 를 넘으면 미끄럼 방지&lt;/strong&gt;를 더한다. &lt;strong&gt;두 숫자를 바꾸거나 20 으로 낮춰 놓는 것&lt;/strong&gt;이 단골이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;경사는 30° 이하&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C23%EC%A1%B0" target="_blank"&gt;제23조(가설통로의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 가설통로를 설치하는 경우 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 견고한 구조로 할 것&lt;br&gt;▶  2. 경사는 30도 &lt;strong&gt;이하로 할 것&lt;/strong&gt;. 다만, 계단을 설치하거나 높이 2미터 미만의 가설통로로서 튼튼한 손잡이를 설치한 경우에는 그러하지 아니하다.&lt;br&gt; 3. 경사가 15도를 초과하는 경우에는 미끄러지지 아니하는 구조로 할 것&lt;br&gt; 4. 추락할 위험이 있는 장소에는 안전난간을 설치할 것. 다만, 작업상 부득이한 경우에는 필요한 부분만 임시로 해체할 수 있다.&lt;br&gt; 5. 수직갱에 가설된 통로의 길이가 15미터 이상인 경우에는 10미터 이내마다 계단참을 설치할 것&lt;br&gt; 6. 건설공사에 사용하는 높이 8미터 이상인 비계다리에는 7미터 이내마다 계단참을 설치할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제23조 — 가설통로의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;30과 15&lt;/strong&gt;를 짝으로 잡는다 — &lt;strong&gt;경사는 30° 까지 허용하되, 15° 를 넘으면 미끄럼 방지&lt;/strong&gt;를 더한다. &lt;strong&gt;두 숫자를 바꾸거나 20으로 낮춰 놓는 것&lt;/strong&gt;이 단골이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;경사는 30° 이하&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C23%EC%A1%B0" target="_blank"&gt;제23조(가설통로의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 가설통로를 설치하는 경우 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 견고한 구조로 할 것&lt;br&gt;▶  2. 경사는 30도 &lt;strong&gt;이하로 할 것&lt;/strong&gt;. 다만, 계단을 설치하거나 높이 2미터 미만의 가설통로로서 튼튼한 손잡이를 설치한 경우에는 그러하지 아니하다.&lt;br&gt; 3. 경사가 15도를 초과하는 경우에는 미끄러지지 아니하는 구조로 할 것&lt;br&gt; 4. 추락할 위험이 있는 장소에는 안전난간을 설치할 것. 다만, 작업상 부득이한 경우에는 필요한 부분만 임시로 해체할 수 있다.&lt;br&gt; 5. 수직갱에 가설된 통로의 길이가 15미터 이상인 경우에는 10미터 이내마다 계단참을 설치할 것&lt;br&gt; 6. 건설공사에 사용하는 높이 8미터 이상인 비계다리에는 7미터 이내마다 계단참을 설치할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -14468,7 +14472,7 @@
       </c>
       <c r="AG104" s="32" t="inlineStr">
         <is>
-          <t>사다리식 통로의 길이가 &lt;strong&gt;10 [m] 이상이면 5 [m] 이내마다&lt;/strong&gt; 계단참을 둔다. 3 [m] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;사다리식 통로의 기준 (규칙 제24조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발판의 간격은 일정하게 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발판과 벽 사이는 15 [cm] 이상 띄울 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭은 30 [cm] 이상으로 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사다리 상단은 걸쳐놓은 지점에서 60 [cm] 이상 올라가게 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;길이가 10 [m] 이상이면 5 [m] 이내마다 계단참을 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3 [m] 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기울기는 75° 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고정식 사다리는 90° 이하&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>사다리식 통로의 길이가 &lt;strong&gt;10 [m] 이상이면 5 [m] 이내마다&lt;/strong&gt; 계단참을 둔다. 3 [m]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;사다리식 통로의 기준 (규칙 제24조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발판의 간격은 일정하게 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발판과 벽 사이는 15 [cm] 이상 띄울 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭은 30 [cm] 이상으로 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사다리 상단은 걸쳐놓은 지점에서 60 [cm] 이상 올라가게 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;길이가 10 [m] 이상이면 5 [m] 이내마다 계단참을 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3 [m]가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기울기는 75° 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고정식 사다리는 90° 이하&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH104" s="32" t="inlineStr">
@@ -14726,17 +14730,17 @@
       </c>
       <c r="AG106" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;매 [㎡] 당 500 [kg] 이상&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;계단의 설치 기준 (규칙 제26조 ~ 제30조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;매 [㎡] 당 500 [kg] 이상&lt;/u&gt; · 안전율 4 이상&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계단참&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 3 [m] 를 초과하면 높이 3 [m] 이내마다 너비 1.2 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 1 [m] 이상이면 개방된 쪽에 안전난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;천장 높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [m] 이내에 장애물이 없을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;매 [㎡] 당 500 [kg] 이상&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;계단의 설치 기준 (규칙 제26조 ~ 제30조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;매 [㎡] 당 500 [kg] 이상&lt;/u&gt; · 안전율 4 이상&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계단참&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 3 [m]를 초과하면 높이 3 [m] 이내마다 너비 1.2 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 1 [m] 이상이면 개방된 쪽에 안전난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;천장 높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [m] 이내에 장애물이 없을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH106" s="32" t="inlineStr">
         <is>
-          <t>① 200 [kg] 은 기준에 못 미친다.&lt;br&gt;② 300 [kg] 도 그렇다.&lt;br&gt;③ 400 [kg] 은 강관비계의 기둥 간 적재하중이다.</t>
+          <t>① 200 [kg]은 기준에 못 미친다.&lt;br&gt;② 300 [kg] 도 그렇다.&lt;br&gt;③ 400 [kg]은 강관비계의 기둥 간 적재하중이다.</t>
         </is>
       </c>
       <c r="AI106" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제26조 — 계단의 강도&lt;/strong&gt;&lt;br&gt;다섯 숫자를 묶어 둔다 — &lt;strong&gt;500 [kg/㎡] · 안전율 4 · 폭 1 [m] · 계단참 3 [m]/1.2 [m] · 천장 2 [m]&lt;/strong&gt;. &lt;strong&gt;400 [kg] 은 비계 쪽의 값&lt;/strong&gt;이라 헷갈리기 쉽다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;계단은 매 [㎡] 당 500 [kg] 이상&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C26%EC%A1%B0" target="_blank"&gt;제26조(계단의 강도)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;▶ ① 사업주는 계단 및 계단참을 설치하는 경우 매제곱미터당 &lt;strong&gt;500킬로그램&lt;/strong&gt; 이상의 하중에 견딜 수 있는 강도를 가진 구조로 설치하여야 하며, 안전율[안전의 정도를 표시하는 것으로서 재료의 파괴응력도(破壞應力度)와 허용응력도(許容應力度)의 비율을 말한다)]은 4 이상으로 하여야 한다.&lt;br&gt;② 사업주는 계단 및 승강구 바닥을 구멍이 있는 재료로 만드는 경우 렌치나 그 밖의 공구 등이 낙하할 위험이 없는 구조로 하여야 한다.&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제26조 — 계단의 강도&lt;/strong&gt;&lt;br&gt;다섯 숫자를 묶어 둔다 — &lt;strong&gt;500 [kg/㎡] · 안전율 4 · 폭 1 [m] · 계단참 3 [m]/1.2 [m] · 천장 2 [m]&lt;/strong&gt;. &lt;strong&gt;400 [kg]은 비계 쪽의 값&lt;/strong&gt;이라 헷갈리기 쉽다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;계단은 매 [㎡] 당 500 [kg] 이상&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C26%EC%A1%B0" target="_blank"&gt;제26조(계단의 강도)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;▶ ① 사업주는 계단 및 계단참을 설치하는 경우 매제곱미터당 &lt;strong&gt;500킬로그램&lt;/strong&gt; 이상의 하중에 견딜 수 있는 강도를 가진 구조로 설치하여야 하며, 안전율[안전의 정도를 표시하는 것으로서 재료의 파괴응력도(破壞應力度)와 허용응력도(許容應力度)의 비율을 말한다)]은 4 이상으로 하여야 한다.&lt;br&gt;② 사업주는 계단 및 승강구 바닥을 구멍이 있는 재료로 만드는 경우 렌치나 그 밖의 공구 등이 낙하할 위험이 없는 구조로 하여야 한다.&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -14855,17 +14859,17 @@
       </c>
       <c r="AG107" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;이음매가 「없는」 것&lt;/strong&gt;은 정상이다. &lt;strong&gt;이음매가 「있는」 것&lt;/strong&gt;이 사용 금지다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;와이어로프의 사용 금지 기준 (규칙 제166조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사용 금지 사유&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이음매가 있는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「없는 것」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한 꼬임에서 끊어진 소선의 수가 10 [%] 이상인 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름의 감소가 공칭지름의 7 [%] 를 초과하는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;꼬인 것 · 심하게 변형되거나 부식된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;열과 전기충격에 의해 손상된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;이음매가 「없는」 것&lt;/strong&gt;은 정상이다. &lt;strong&gt;이음매가 「있는」 것&lt;/strong&gt;이 사용 금지다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;와이어로프의 사용 금지 기준 (규칙 제166조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사용 금지 사유&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이음매가 있는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「없는 것」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한 꼬임에서 끊어진 소선의 수가 10 [%] 이상인 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름의 감소가 공칭지름의 7 [%]를 초과하는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;꼬인 것 · 심하게 변형되거나 부식된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;열과 전기충격에 의해 손상된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH107" s="32" t="inlineStr">
         <is>
-          <t>② 지름의 감소가 공칭지름의 7 [%] 를 초과하는 것은 사용 금지다.&lt;br&gt;③ 꼬인 것도 그렇다.&lt;br&gt;④ 열과 전기충격에 의해 손상된 것도 그렇다.</t>
+          <t>② 지름의 감소가 공칭지름의 7 [%]를 초과하는 것은 사용 금지다.&lt;br&gt;③ 꼬인 것도 그렇다.&lt;br&gt;④ 열과 전기충격에 의해 손상된 것도 그렇다.</t>
         </is>
       </c>
       <c r="AI107" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제166조 — 와이어로프의 사용 금지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「있는」과 「없는」&lt;/strong&gt; 한 글자를 뒤집어 놓은 문항이다. &lt;strong&gt;이음매는 그 자리에서 끊어지기 쉬워&lt;/strong&gt; 양중용 로프에는 허용하지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;이음매가 「있는」 것이 금지&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C166%EC%A1%B0" target="_blank"&gt;제166조(이음매가 있는 와이어로프 등의 사용 금지)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;제166조(이음매가 있는 와이어로프 등의 사용 금지) 와이어 로프의 사용에 관하여는 제63조제1항제1호를 준용한다. 이 경우 "달비계"는 "양중기"로 본다. &amp;lt;개정 2021.11.19, 2022.10.18&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제166조 — 와이어로프의 사용 금지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「있는」과 「없는」&lt;/strong&gt;한 글자를 뒤집어 놓은 문항이다. &lt;strong&gt;이음매는 그 자리에서 끊어지기 쉬워&lt;/strong&gt; 양중용 로프에는 허용하지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;이음매가 「있는」 것이 금지&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C166%EC%A1%B0" target="_blank"&gt;제166조(이음매가 있는 와이어로프 등의 사용 금지)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;제166조(이음매가 있는 와이어로프 등의 사용 금지) 와이어 로프의 사용에 관하여는 제63조제1항제1호를 준용한다. 이 경우 "달비계"는 "양중기"로 본다. &amp;lt;개정 2021.11.19, 2022.10.18&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -14984,12 +14988,12 @@
       </c>
       <c r="AG108" s="32" t="inlineStr">
         <is>
-          <t>현행 기준으로 &lt;strong&gt;연암 및 풍화암은 1 : 1.0&lt;/strong&gt;이므로 연직 2 [m] 면 수평도 &lt;strong&gt;2.0 [m]&lt;/strong&gt;이 된다. 다만 &lt;strong&gt;옛 기준(연암 1 : 0.5)&lt;/strong&gt;으로 풀면 $2 \times 0.5 = 1.0$ [m] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;굴착면의 기울기 — 옛 기준과 현행&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지반의 종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;옛 기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;현행 기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;모래&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 1.8&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 1.8&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연암&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 0.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 1.0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;풍화암과 통합&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;풍화암&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 0.8&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 1.0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경암&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 0.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 0.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그 밖의 흙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;보통흙 습지·건지로 구분&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 1.2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>현행 기준으로 &lt;strong&gt;연암 및 풍화암은 1 : 1.0&lt;/strong&gt;이므로 연직 2 [m] 면 수평도 &lt;strong&gt;2.0 [m]&lt;/strong&gt;이 된다. 다만 &lt;strong&gt;옛 기준(연암 1 : 0.5)&lt;/strong&gt;으로 풀면 $2 \times 0.5 = 1.0$ [m]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;굴착면의 기울기 — 옛 기준과 현행&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지반의 종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;옛 기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;현행 기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;모래&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 1.8&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 1.8&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연암&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 0.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 1.0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;풍화암과 통합&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;풍화암&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 0.8&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 1.0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경암&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 0.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 0.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그 밖의 흙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;보통흙 습지·건지로 구분&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 1.2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH108" s="32" t="inlineStr">
         <is>
-          <t>① 2.0 [m] 는 현행 기준(1 : 1.0)으로 푼 값이다.&lt;br&gt;② 1.5 [m] 는 어느 기준에도 맞지 않는다.&lt;br&gt;④ 0.5 [m] 도 그렇다.</t>
+          <t>① 2.0 [m]는 현행 기준(1 : 1.0)으로 푼 값이다.&lt;br&gt;② 1.5 [m]는 어느 기준에도 맞지 않는다.&lt;br&gt;④ 0.5 [m] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI108" s="32" t="inlineStr">
@@ -16403,7 +16407,7 @@
       </c>
       <c r="AG119" s="32" t="inlineStr">
         <is>
-          <t>점화회선은 &lt;strong&gt;다른 동력선·조명회선과 완전히 분리&lt;/strong&gt; 해야 한다. 한곳에 모으면 &lt;strong&gt;유도전류로 뜻하지 않게 터질 수&lt;/strong&gt; 있다.</t>
+          <t>점화회선은 &lt;strong&gt;다른 동력선·조명회선과 완전히 분리&lt;/strong&gt;해야 한다. 한곳에 모으면 &lt;strong&gt;유도전류로 뜻하지 않게 터질 수&lt;/strong&gt; 있다.</t>
         </is>
       </c>
       <c r="AH119" s="32" t="inlineStr">
@@ -16542,7 +16546,7 @@
       </c>
       <c r="AI120" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;비계의 좌굴 방지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;기둥의 좌굴 하중은 길이의 제곱에 반비례&lt;/strong&gt; 한다. &lt;strong&gt;수평재로 중간을 붙들어 「자유 길이」를 절반으로 줄이면 좌굴 하중은 네 배&lt;/strong&gt;가 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수평재와 가새는 좌굴 방지&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;비계의 좌굴 방지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;기둥의 좌굴 하중은 길이의 제곱에 반비례&lt;/strong&gt;한다. &lt;strong&gt;수평재로 중간을 붙들어 「자유 길이」를 절반으로 줄이면 좌굴 하중은 네 배&lt;/strong&gt;가 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수평재와 가새는 좌굴 방지&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16661,12 +16665,12 @@
       </c>
       <c r="AG121" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;이음매가 없는 것&lt;/strong&gt;만 쓸 수 있다. 나머지 셋은 모두 사용 금지에 해당한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;와이어로프의 사용 금지 기준 (규칙 제63조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사용 금지 사유&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기와의 대응&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이음매가 있는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②는 「없는 것」이라 쓸 수 있다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한 꼬임에서 끊어진 소선의 수가 10 [%] 이상인 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④는 10 [%] 라 해당&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름의 감소가 공칭지름의 7 [%] 를 초과하는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①은 8 [%] 라 해당&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;꼬인 것 · 심하게 변형되거나 부식된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③이 해당&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;이음매가 없는 것&lt;/strong&gt;만 쓸 수 있다. 나머지 셋은 모두 사용 금지에 해당한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;와이어로프의 사용 금지 기준 (규칙 제63조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사용 금지 사유&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기와의 대응&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이음매가 있는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②는 「없는 것」이라 쓸 수 있다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한 꼬임에서 끊어진 소선의 수가 10 [%] 이상인 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④는 10 [%] 라 해당&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름의 감소가 공칭지름의 7 [%]를 초과하는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①은 8 [%] 라 해당&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;꼬인 것 · 심하게 변형되거나 부식된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③이 해당&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH121" s="32" t="inlineStr">
         <is>
-          <t>① 지름의 감소가 8 [%] 면 7 [%] 를 넘으므로 사용 금지다.&lt;br&gt;③ 심하게 변형되거나 부식된 것도 사용 금지다.&lt;br&gt;④ 끊어진 소선이 10 [%] 면 「10 [%] 이상」에 들어 사용 금지다.</t>
+          <t>① 지름의 감소가 8 [%] 면 7 [%]를 넘으므로 사용 금지다.&lt;br&gt;③ 심하게 변형되거나 부식된 것도 사용 금지다.&lt;br&gt;④ 끊어진 소선이 10 [%] 면 「10 [%] 이상」에 들어 사용 금지다.</t>
         </is>
       </c>
       <c r="AI121" s="32" t="inlineStr">
@@ -16790,17 +16794,17 @@
       </c>
       <c r="AG122" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;맨 윗부분에서 31 [m] 되는 지점 아래&lt;/strong&gt;를 2개로 묶는다. $52 - 31 = 21$ [m] 이므로 &lt;strong&gt;지상에서 21 [m] 까지&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;강관비계의 숫자&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 간격 — 띠장 방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.85 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 간격 — 장선 방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.5 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;띠장 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.0 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 간 적재하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;400 [kg] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;묶어 세우는 구간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;맨 윗부분에서 31 [m] 되는 지점 아래&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;맨 윗부분에서 31 [m] 되는 지점 아래&lt;/strong&gt;를 2개로 묶는다. $52 - 31 = 21$ [m]이므로 &lt;strong&gt;지상에서 21 [m]까지&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;강관비계의 숫자&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 간격 — 띠장 방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.85 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 간격 — 장선 방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.5 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;띠장 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.0 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 간 적재하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;400 [kg] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;묶어 세우는 구간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;맨 윗부분에서 31 [m] 되는 지점 아래&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH122" s="32" t="inlineStr">
         <is>
-          <t>① 11 [m] 는 계산과 맞지 않는다.&lt;br&gt;② 16 [m] 도 맞지 않는다.&lt;br&gt;④ 26 [m] 도 맞지 않는다.</t>
+          <t>① 11 [m]는 계산과 맞지 않는다.&lt;br&gt;② 16 [m] 도 맞지 않는다.&lt;br&gt;④ 26 [m] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI122" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제60조 — 강관비계의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「위에서부터 31 [m]」&lt;/strong&gt;라는 점이 갈림길이다. &lt;strong&gt;아래쪽이 무거운 하중을 받으므로 밑둥을 튼튼하게&lt;/strong&gt; 하는 것이다. &lt;strong&gt;전체 높이에서 31 을 빼면&lt;/strong&gt; 곧바로 답이 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전체 높이 − 31 [m]&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C60%EC%A1%B0" target="_blank"&gt;제60조(강관비계의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 강관을 사용하여 비계를 구성하는 경우 다음 각 호의 사항을 준수해야 한다. &amp;lt;개정 2012.5.31, 2019.10.15, 2019.12.26, 2023.11.14&amp;gt;&lt;br&gt; 1. 비계기둥의 간격은 띠장 방향에서는 1.85미터 이하, 장선(長線) 방향에서는 1.5미터 이하로 할 것. 다만, 다음 각 목의 어느 하나에 해당하는 작업의 경우에는 안전성에 대한 구조검토를 실시하고 조립도를 작성하면 띠장 방향 및 장선 방향으로 각각 2.7미터 이하로 할 수 있다.&lt;br&gt; 가. 선박 및 보트 건조작업&lt;br&gt; 나. 그 밖에 장비 반입ㆍ반출을 위하여 공간 등을 확보할 필요가 있는 등 작업의 성질상 비계기둥 간격에 관한 기준을 준수하기 곤란한 작업&lt;br&gt; 2. 띠장 간격은 2.0미터 이하로 할 것. 다만, 작업의 성질상 이를 준수하기가 곤란하여 쌍기둥틀 등에 의하여 해당 부분을 보강한 경우에는 그러하지 아니하다.&lt;br&gt; 3. 비계기둥의 제일 윗부분으로부터 31미터되는 지점 밑부분의 비계기둥은 2개의 강관으로 묶어 세울 것. 다만, 브라켓(bracket, 까치발) 등으로 보강하여 2개의 강관으로 묶을 경우 이상의 강도가 유지되는 경우에는 그러하지 아니하다.&lt;br&gt; 4. 비계기둥 간의 적재하중은 400킬로그램을 초과하지 않도록 할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제60조 — 강관비계의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「위에서부터 31 [m]」&lt;/strong&gt;라는 점이 갈림길이다. &lt;strong&gt;아래쪽이 무거운 하중을 받으므로 밑둥을 튼튼하게&lt;/strong&gt; 하는 것이다. &lt;strong&gt;전체 높이에서 31을 빼면&lt;/strong&gt; 곧바로 답이 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전체 높이 − 31 [m]&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C60%EC%A1%B0" target="_blank"&gt;제60조(강관비계의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 강관을 사용하여 비계를 구성하는 경우 다음 각 호의 사항을 준수해야 한다. &amp;lt;개정 2012.5.31, 2019.10.15, 2019.12.26, 2023.11.14&amp;gt;&lt;br&gt; 1. 비계기둥의 간격은 띠장 방향에서는 1.85미터 이하, 장선(長線) 방향에서는 1.5미터 이하로 할 것. 다만, 다음 각 목의 어느 하나에 해당하는 작업의 경우에는 안전성에 대한 구조검토를 실시하고 조립도를 작성하면 띠장 방향 및 장선 방향으로 각각 2.7미터 이하로 할 수 있다.&lt;br&gt; 가. 선박 및 보트 건조작업&lt;br&gt; 나. 그 밖에 장비 반입ㆍ반출을 위하여 공간 등을 확보할 필요가 있는 등 작업의 성질상 비계기둥 간격에 관한 기준을 준수하기 곤란한 작업&lt;br&gt; 2. 띠장 간격은 2.0미터 이하로 할 것. 다만, 작업의 성질상 이를 준수하기가 곤란하여 쌍기둥틀 등에 의하여 해당 부분을 보강한 경우에는 그러하지 아니하다.&lt;br&gt; 3. 비계기둥의 제일 윗부분으로부터 31미터되는 지점 밑부분의 비계기둥은 2개의 강관으로 묶어 세울 것. 다만, 브라켓(bracket, 까치발) 등으로 보강하여 2개의 강관으로 묶을 경우 이상의 강도가 유지되는 경우에는 그러하지 아니하다.&lt;br&gt; 4. 비계기둥 간의 적재하중은 400킬로그램을 초과하지 않도록 할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
